--- a/Cplusplus/Cplusplus.xlsx
+++ b/Cplusplus/Cplusplus.xlsx
@@ -9,10 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="CheckList C++" sheetId="1" r:id="rId1"/>
+    <sheet name="C++ FOUNDATIONS" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="1255">
   <si>
     <t>[ ] Branching strategies (gitflow, feature branches)</t>
   </si>
@@ -3695,13 +3696,1990 @@
   </si>
   <si>
     <t>C++ FOUNDATIONS</t>
+  </si>
+  <si>
+    <t>1. BASIC SYNTAX &amp; DATA TYPES</t>
+  </si>
+  <si>
+    <t>1.1 Primitive Types</t>
+  </si>
+  <si>
+    <t>int, float, double, char, bool</t>
+  </si>
+  <si>
+    <t>// Các kiểu dữ liệu cơ bản</t>
+  </si>
+  <si>
+    <t>int age = 25;              // Số nguyên: -2,147,483,648 đến 2,147,483,647</t>
+  </si>
+  <si>
+    <t>float price = 19.99f;      // Số thực độ chính xác đơn (4 bytes)</t>
+  </si>
+  <si>
+    <t>double pi = 3.14159265359; // Số thực độ chính xác kép (8 bytes)</t>
+  </si>
+  <si>
+    <t>char grade = 'A';          // Ký tự đơn (1 byte)</t>
+  </si>
+  <si>
+    <t>bool isValid = true;       // Giá trị logic: true/false</t>
+  </si>
+  <si>
+    <t>Khi nào dùng gì:</t>
+  </si>
+  <si>
+    <t>signed vs unsigned</t>
+  </si>
+  <si>
+    <t>signed int a = -100;      // Có thể âm: -2^31 đến 2^31-1</t>
+  </si>
+  <si>
+    <t>unsigned int b = 100;     // Chỉ dương: 0 đến 2^32-1</t>
+  </si>
+  <si>
+    <t>// BẪY PHỔ BIẾN: Unsigned underflow</t>
+  </si>
+  <si>
+    <t>unsigned int count = 0;</t>
+  </si>
+  <si>
+    <t>count--;                  // count = 4,294,967,295 (wrap around!)</t>
+  </si>
+  <si>
+    <t>Nguyên tắc:</t>
+  </si>
+  <si>
+    <t>// BẪY: So sánh signed và unsigned</t>
+  </si>
+  <si>
+    <t>int x = -1;</t>
+  </si>
+  <si>
+    <t>unsigned int y = 1;</t>
+  </si>
+  <si>
+    <t>if (x &lt; y) // FALSE! x được convert thành unsigned rất lớn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; "Unexpected!";</t>
+  </si>
+  <si>
+    <t>Type Casting</t>
+  </si>
+  <si>
+    <t>// static_cast: Chuyển đổi rõ ràng, an toàn tại compile-time</t>
+  </si>
+  <si>
+    <t>double d = 3.14;</t>
+  </si>
+  <si>
+    <t>int i = static_cast&lt;int&gt;(d);  // i = 3 (cắt phần thập phân)</t>
+  </si>
+  <si>
+    <t>// dynamic_cast: Chuyển đổi trong inheritance, kiểm tra runtime</t>
+  </si>
+  <si>
+    <t>class Base { virtual void f() {} };</t>
+  </si>
+  <si>
+    <t>class Derived : public Base {};</t>
+  </si>
+  <si>
+    <t>Base* b = new Derived();</t>
+  </si>
+  <si>
+    <t>Derived* d = dynamic_cast&lt;Derived*&gt;(b); // An toàn, trả nullptr nếu fail</t>
+  </si>
+  <si>
+    <t>// const_cast: Bỏ const (nguy hiểm!)</t>
+  </si>
+  <si>
+    <t>const int* ptr = &amp;i;</t>
+  </si>
+  <si>
+    <t>int* modifiable = const_cast&lt;int*&gt;(ptr);</t>
+  </si>
+  <si>
+    <t>// reinterpret_cast: Chuyển đổi kiểu con trỏ (rất nguy hiểm)</t>
+  </si>
+  <si>
+    <t>int* p = new int(65);</t>
+  </si>
+  <si>
+    <t>char* ch = reinterpret_cast&lt;char*&gt;(p); // Đọc bytes thô</t>
+  </si>
+  <si>
+    <t>Ứng dụng thực tế:</t>
+  </si>
+  <si>
+    <t>sizeof Operator</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; sizeof(int);        // 4 bytes (phụ thuộc platform)</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; sizeof(double);     // 8 bytes</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; sizeof(char);       // 1 byte (luôn luôn)</t>
+  </si>
+  <si>
+    <t>int arr[10];</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; sizeof(arr);        // 40 bytes (10 * 4)</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; sizeof(arr)/sizeof(arr[0]); // Số phần tử: 10</t>
+  </si>
+  <si>
+    <t>// Với con trỏ</t>
+  </si>
+  <si>
+    <t>int* ptr = arr;</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; sizeof(ptr);        // 8 bytes (trên 64-bit), NOT 40!</t>
+  </si>
+  <si>
+    <t>1.2 Variables &amp; Constants</t>
+  </si>
+  <si>
+    <t>const và constexpr</t>
+  </si>
+  <si>
+    <t>// const: Giá trị không đổi tại runtime</t>
+  </si>
+  <si>
+    <t>const int MAX_USERS = 100;</t>
+  </si>
+  <si>
+    <t>const double PI = 3.14159;</t>
+  </si>
+  <si>
+    <t>// constexpr: Tính toán tại compile-time (C++11)</t>
+  </si>
+  <si>
+    <t>constexpr int square(int x) { return x * x; }</t>
+  </si>
+  <si>
+    <t>constexpr int result = square(5); // Tính lúc compile</t>
+  </si>
+  <si>
+    <t>// Ứng dụng</t>
+  </si>
+  <si>
+    <t>const int size = getUserInput();      // OK, xác định runtime</t>
+  </si>
+  <si>
+    <t>constexpr int size2 = getUserInput(); // ERROR! Phải biết compile-time</t>
+  </si>
+  <si>
+    <t>Khi nào dùng:</t>
+  </si>
+  <si>
+    <t>#define vs const</t>
+  </si>
+  <si>
+    <t>// #define: Macro, thay thế text trước compile</t>
+  </si>
+  <si>
+    <t>#define PI 3.14159</t>
+  </si>
+  <si>
+    <t>#define MAX(a,b) ((a)&gt;(b)?(a):(b))</t>
+  </si>
+  <si>
+    <t>// const: Biến thực sự, có type safety</t>
+  </si>
+  <si>
+    <t>// BẪY với #define</t>
+  </si>
+  <si>
+    <t>#define SQUARE(x) x*x</t>
+  </si>
+  <si>
+    <t>int result = SQUARE(2+3); // Expand thành: 2+3*2+3 = 11 (WRONG!)</t>
+  </si>
+  <si>
+    <t>// Đúng với const/constexpr</t>
+  </si>
+  <si>
+    <t>constexpr int square(int x) { return x*x; }</t>
+  </si>
+  <si>
+    <t>int result = square(2+3); // = 25 (CORRECT!)</t>
+  </si>
+  <si>
+    <t>Literal Types</t>
+  </si>
+  <si>
+    <t>int decimal = 42;</t>
+  </si>
+  <si>
+    <t>int hex = 0x2A;           // Hexadecimal</t>
+  </si>
+  <si>
+    <t>int binary = 0b101010;    // Binary (C++14)</t>
+  </si>
+  <si>
+    <t>int octal = 052;          // Octal (ít dùng)</t>
+  </si>
+  <si>
+    <t>char c = 'A';             // Character literal</t>
+  </si>
+  <si>
+    <t>char newline = '\n';      // Escape sequence</t>
+  </si>
+  <si>
+    <t>// Suffixes</t>
+  </si>
+  <si>
+    <t>float f = 3.14f;          // f = float</t>
+  </si>
+  <si>
+    <t>long l = 123L;            // L = long</t>
+  </si>
+  <si>
+    <t>unsigned u = 123U;        // U = unsigned</t>
+  </si>
+  <si>
+    <t>long long ll = 123LL;     // LL = long long</t>
+  </si>
+  <si>
+    <t>2. CONTROL FLOW</t>
+  </si>
+  <si>
+    <t>2.1 Loops</t>
+  </si>
+  <si>
+    <t>for, while, do-while</t>
+  </si>
+  <si>
+    <t>// for: Biết trước số lần lặp</t>
+  </si>
+  <si>
+    <t>for (int i = 0; i &lt; 10; i++) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; i &lt;&lt; " ";</t>
+  </si>
+  <si>
+    <t>}</t>
+  </si>
+  <si>
+    <t>// while: Lặp khi điều kiện đúng</t>
+  </si>
+  <si>
+    <t>int count = 0;</t>
+  </si>
+  <si>
+    <t>while (count &lt; 10) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; count++;</t>
+  </si>
+  <si>
+    <t>// do-while: Luôn chạy ít nhất 1 lần</t>
+  </si>
+  <si>
+    <t>int input;</t>
+  </si>
+  <si>
+    <t>do {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; "Enter positive number: ";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cin &gt;&gt; input;</t>
+  </si>
+  <si>
+    <t>} while (input &lt;= 0);</t>
+  </si>
+  <si>
+    <t>Ứng dụng:</t>
+  </si>
+  <si>
+    <t>Range-based for (C++11)</t>
+  </si>
+  <si>
+    <t>vector&lt;int&gt; nums = {1, 2, 3, 4, 5};</t>
+  </si>
+  <si>
+    <t>// Đọc giá trị</t>
+  </si>
+  <si>
+    <t>for (int n : nums) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; n &lt;&lt; " ";</t>
+  </si>
+  <si>
+    <t>// Sửa giá trị (phải dùng reference!)</t>
+  </si>
+  <si>
+    <t>for (int&amp; n : nums) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    n *= 2;  // Nhân đôi mỗi phần tử</t>
+  </si>
+  <si>
+    <t>// auto: Tự suy kiểu</t>
+  </si>
+  <si>
+    <t>for (auto&amp; item : nums) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    item += 10;</t>
+  </si>
+  <si>
+    <t>// const auto&amp;: Đọc hiệu quả (không copy)</t>
+  </si>
+  <si>
+    <t>for (const auto&amp; str : stringVector) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; str &lt;&lt; endl;</t>
+  </si>
+  <si>
+    <t>BẪY phổ biến:</t>
+  </si>
+  <si>
+    <t>// SAI: Quên &amp;, bị copy</t>
+  </si>
+  <si>
+    <t>for (auto item : largeVector) {  // Copy mỗi phần tử!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    process(item);</t>
+  </si>
+  <si>
+    <t>// ĐÚNG: Dùng const reference</t>
+  </si>
+  <si>
+    <t>for (const auto&amp; item : largeVector) {</t>
+  </si>
+  <si>
+    <t>break, continue, return</t>
+  </si>
+  <si>
+    <t>// break: Thoát khỏi loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (i == 5) break;  // Dừng tại i=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; i;</t>
+  </si>
+  <si>
+    <t>// continue: Bỏ qua iteration hiện tại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (i % 2 == 0) continue;  // Bỏ qua số chẵn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; i;  // In số lẻ</t>
+  </si>
+  <si>
+    <t>// return: Thoát khỏi function</t>
+  </si>
+  <si>
+    <t>int findIndex(vector&lt;int&gt;&amp; v, int target) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    for (int i = 0; i &lt; v.size(); i++) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if (v[i] == target) return i;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return -1;  // Không tìm thấy</t>
+  </si>
+  <si>
+    <t>2.2 Conditionals</t>
+  </si>
+  <si>
+    <t>if-else, switch-case</t>
+  </si>
+  <si>
+    <t>// if-else</t>
+  </si>
+  <si>
+    <t>int score = 85;</t>
+  </si>
+  <si>
+    <t>if (score &gt;= 90) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; "A";</t>
+  </si>
+  <si>
+    <t>} else if (score &gt;= 80) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; "B";</t>
+  </si>
+  <si>
+    <t>} else {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; "C";</t>
+  </si>
+  <si>
+    <t>// switch-case: Hiệu quả với nhiều giá trị cụ thể</t>
+  </si>
+  <si>
+    <t>char grade = 'B';</t>
+  </si>
+  <si>
+    <t>switch (grade) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case 'A':</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        cout &lt;&lt; "Excellent";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        break;  // BẪY: Quên break gây fall-through!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case 'B':</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case 'C':</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        cout &lt;&lt; "Good";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        break;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    default:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        cout &lt;&lt; "Needs improvement";</t>
+  </si>
+  <si>
+    <t>BẪY fall-through:</t>
+  </si>
+  <si>
+    <t>switch (x) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case 1:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        doSomething();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // Quên break!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case 2:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        doOtherThing();  // Cũng chạy khi x=1!</t>
+  </si>
+  <si>
+    <t>Ternary Operator</t>
+  </si>
+  <si>
+    <t>// condition ? true_value : false_value</t>
+  </si>
+  <si>
+    <t>int age = 20;</t>
+  </si>
+  <si>
+    <t>string status = (age &gt;= 18) ? "Adult" : "Minor";</t>
+  </si>
+  <si>
+    <t>// Nested (tránh lạm dụng!)</t>
+  </si>
+  <si>
+    <t>int score = 75;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string grade = (score &gt;= 90) ? "A" : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">               (score &gt;= 80) ? "B" : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">               (score &gt;= 70) ? "C" : "F";</t>
+  </si>
+  <si>
+    <t>Short-circuit Evaluation</t>
+  </si>
+  <si>
+    <t>// &amp;&amp; (AND): Dừng khi gặp false</t>
+  </si>
+  <si>
+    <t>if (ptr != nullptr &amp;&amp; ptr-&gt;value &gt; 10) {  // An toàn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // ptr-&gt;value chỉ chạy khi ptr != nullptr</t>
+  </si>
+  <si>
+    <t>// || (OR): Dừng khi gặp true</t>
+  </si>
+  <si>
+    <t>if (isValid() || fallbackCheck()) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // fallbackCheck() không chạy nếu isValid() = true</t>
+  </si>
+  <si>
+    <t>// Ứng dụng: Tránh null pointer</t>
+  </si>
+  <si>
+    <t>Node* node = getNode();</t>
+  </si>
+  <si>
+    <t>if (node &amp;&amp; node-&gt;next &amp;&amp; node-&gt;next-&gt;data == target) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // An toàn, check từng cấp</t>
+  </si>
+  <si>
+    <t>3. FUNCTIONS</t>
+  </si>
+  <si>
+    <t>3.1 Function Basics</t>
+  </si>
+  <si>
+    <t>Declaration vs Definition</t>
+  </si>
+  <si>
+    <t>// Declaration (prototype) - trong header file</t>
+  </si>
+  <si>
+    <t>int add(int a, int b);</t>
+  </si>
+  <si>
+    <t>// Definition - trong .cpp file</t>
+  </si>
+  <si>
+    <t>int add(int a, int b) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return a + b;</t>
+  </si>
+  <si>
+    <t>// Hoặc cả hai cùng lúc</t>
+  </si>
+  <si>
+    <t>int multiply(int a, int b) { return a * b; }</t>
+  </si>
+  <si>
+    <t>Parameter Passing</t>
+  </si>
+  <si>
+    <t>// By value: Copy giá trị (thay đổi không ảnh hưởng bên ngoài)</t>
+  </si>
+  <si>
+    <t>void increment(int x) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    x++;  // Chỉ thay đổi local copy</t>
+  </si>
+  <si>
+    <t>// By reference: Trỏ đến biến gốc</t>
+  </si>
+  <si>
+    <t>void incrementRef(int&amp; x) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    x++;  // Thay đổi biến gốc</t>
+  </si>
+  <si>
+    <t>// By pointer: Truyền địa chỉ</t>
+  </si>
+  <si>
+    <t>void incrementPtr(int* x) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    (*x)++;  // Dereference và tăng</t>
+  </si>
+  <si>
+    <t>// Ví dụ sử dụng</t>
+  </si>
+  <si>
+    <t>int num = 5;</t>
+  </si>
+  <si>
+    <t>increment(num);      // num = 5 (không đổi)</t>
+  </si>
+  <si>
+    <t>incrementRef(num);   // num = 6 (thay đổi)</t>
+  </si>
+  <si>
+    <t>incrementPtr(&amp;num);  // num = 7 (thay đổi)</t>
+  </si>
+  <si>
+    <t>// const reference: Hiệu quả cho object lớn, không cho sửa</t>
+  </si>
+  <si>
+    <t>void print(const string&amp; str) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; str;  // Không copy, không sửa được str</t>
+  </si>
+  <si>
+    <t>By value: Kiểu nhỏ (int, char), không cần modify</t>
+  </si>
+  <si>
+    <t>By reference: Modify biến gốc, object lớn</t>
+  </si>
+  <si>
+    <t>const reference: Object lớn, chỉ đọc (string, vector)</t>
+  </si>
+  <si>
+    <t>By pointer: Cần kiểm tra nullptr, C-style API</t>
+  </si>
+  <si>
+    <t>Default Parameters</t>
+  </si>
+  <si>
+    <t>// Default phải ở cuối danh sách tham số</t>
+  </si>
+  <si>
+    <t>void greet(string name, string greeting = "Hello") {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; greeting &lt;&lt; ", " &lt;&lt; name &lt;&lt; endl;</t>
+  </si>
+  <si>
+    <t>greet("Alice");              // "Hello, Alice"</t>
+  </si>
+  <si>
+    <t>greet("Bob", "Hi");          // "Hi, Bob"</t>
+  </si>
+  <si>
+    <t>// BẪY: Default ở đầu (ERROR!)</t>
+  </si>
+  <si>
+    <t>void wrong(int x = 5, int y) {}  // Compile error!</t>
+  </si>
+  <si>
+    <t>Function Overloading</t>
+  </si>
+  <si>
+    <t>// Cùng tên, khác tham số</t>
+  </si>
+  <si>
+    <t>int add(int a, int b) { return a + b; }</t>
+  </si>
+  <si>
+    <t>double add(double a, double b) { return a + b; }</t>
+  </si>
+  <si>
+    <t>string add(string a, string b) { return a + b; }</t>
+  </si>
+  <si>
+    <t>// Compiler chọn version phù hợp</t>
+  </si>
+  <si>
+    <t>add(1, 2);          // Gọi int version</t>
+  </si>
+  <si>
+    <t>add(1.5, 2.5);      // Gọi double version</t>
+  </si>
+  <si>
+    <t>add("Hello", "!");  // Gọi string version</t>
+  </si>
+  <si>
+    <t>// BẪY: Ambiguous overload</t>
+  </si>
+  <si>
+    <t>void print(int x) {}</t>
+  </si>
+  <si>
+    <t>void print(double x) {}</t>
+  </si>
+  <si>
+    <t>print(5);    // OK - int</t>
+  </si>
+  <si>
+    <t>print(5.0);  // OK - double</t>
+  </si>
+  <si>
+    <t>print('A');  // ERROR! char có thể convert sang cả int và double</t>
+  </si>
+  <si>
+    <t>3.2 Advanced Function Features</t>
+  </si>
+  <si>
+    <t>inline Functions</t>
+  </si>
+  <si>
+    <t>// Gợi ý compiler thay thế code tại chỗ gọi (tránh overhead)</t>
+  </si>
+  <si>
+    <t>inline int max(int a, int b) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return (a &gt; b) ? a : b;</t>
+  </si>
+  <si>
+    <t>// Compiler có thể bỏ qua nếu function phức tạp</t>
+  </si>
+  <si>
+    <t>// Modern compiler thường tự inline, không cần keyword</t>
+  </si>
+  <si>
+    <t>Khi dùng:</t>
+  </si>
+  <si>
+    <t>Function nhỏ, gọi nhiều lần (getter/setter)</t>
+  </si>
+  <si>
+    <t>Performance-critical code</t>
+  </si>
+  <si>
+    <t>Header-only libraries</t>
+  </si>
+  <si>
+    <t>Function Pointers</t>
+  </si>
+  <si>
+    <t>// Con trỏ hàm: Trỏ đến địa chỉ function</t>
+  </si>
+  <si>
+    <t>int subtract(int a, int b) { return a - b; }</t>
+  </si>
+  <si>
+    <t>// Khai báo: return_type (*pointer_name)(params)</t>
+  </si>
+  <si>
+    <t>int (*operation)(int, int);</t>
+  </si>
+  <si>
+    <t>operation = add;</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; operation(5, 3);  // 8</t>
+  </si>
+  <si>
+    <t>operation = subtract;</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; operation(5, 3);  // 2</t>
+  </si>
+  <si>
+    <t>// Ứng dụng: Callback functions</t>
+  </si>
+  <si>
+    <t>void process(int arr[], int size, int (*func)(int)) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    for (int i = 0; i &lt; size; i++) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        arr[i] = func(arr[i]);</t>
+  </si>
+  <si>
+    <t>int square(int x) { return x * x; }</t>
+  </si>
+  <si>
+    <t>int arr[] = {1, 2, 3};</t>
+  </si>
+  <si>
+    <t>process(arr, 3, square);  // arr = {1, 4, 9}</t>
+  </si>
+  <si>
+    <t>Lambda Expressions (C++11)</t>
+  </si>
+  <si>
+    <t>// Syntax: [capture](params) -&gt; return_type { body }</t>
+  </si>
+  <si>
+    <t>auto add = [](int a, int b) { return a + b; };</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; add(3, 4);  // 7</t>
+  </si>
+  <si>
+    <t>// Capture variables</t>
+  </si>
+  <si>
+    <t>int multiplier = 10;</t>
+  </si>
+  <si>
+    <t>auto multiply = [multiplier](int x) { return x * multiplier; };</t>
+  </si>
+  <si>
+    <t>// Capture modes:</t>
+  </si>
+  <si>
+    <t>// [] : Không capture</t>
+  </si>
+  <si>
+    <t>// [x] : Capture x by value</t>
+  </si>
+  <si>
+    <t>// [&amp;x] : Capture x by reference</t>
+  </si>
+  <si>
+    <t>// [=] : Capture tất cả by value</t>
+  </si>
+  <si>
+    <t>// [&amp;] : Capture tất cả by reference</t>
+  </si>
+  <si>
+    <t>// Ứng dụng với STL algorithms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auto it = find_if(nums.begin(), nums.end(), </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                  [](int n) { return n &gt; 3; });</t>
+  </si>
+  <si>
+    <t>// Sort với custom comparator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sort(nums.begin(), nums.end(), </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     [](int a, int b) { return a &gt; b; });  // Giảm dần</t>
+  </si>
+  <si>
+    <t>BẪY với capture:</t>
+  </si>
+  <si>
+    <t>int x = 5;</t>
+  </si>
+  <si>
+    <t>auto bad = [x]() mutable { x++; };  // Chỉ thay đổi copy</t>
+  </si>
+  <si>
+    <t>bad();  // x = 5 (không đổi)</t>
+  </si>
+  <si>
+    <t>auto good = [&amp;x]() { x++; };  // Thay đổi biến gốc</t>
+  </si>
+  <si>
+    <t>good();  // x = 6</t>
+  </si>
+  <si>
+    <t>std::function (C++11)</t>
+  </si>
+  <si>
+    <t>#include &lt;functional&gt;</t>
+  </si>
+  <si>
+    <t>// Wrapper generic cho mọi callable (function, lambda, functor)</t>
+  </si>
+  <si>
+    <t>function&lt;int(int, int)&gt; op;</t>
+  </si>
+  <si>
+    <t>op = [](int a, int b) { return a + b; };</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; op(3, 4);  // 7</t>
+  </si>
+  <si>
+    <t>op = [](int a, int b) { return a * b; };</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; op(3, 4);  // 12</t>
+  </si>
+  <si>
+    <t>// Ứng dụng: Lưu trữ callbacks</t>
+  </si>
+  <si>
+    <t>class EventHandler {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    vector&lt;function&lt;void(string)&gt;&gt; listeners;</t>
+  </si>
+  <si>
+    <t>public:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void subscribe(function&lt;void(string)&gt; callback) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        listeners.push_back(callback);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void notify(string event) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        for (auto&amp; listener : listeners)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            listener(event);</t>
+  </si>
+  <si>
+    <t>};</t>
+  </si>
+  <si>
+    <t>4. ARRAYS &amp; STRINGS</t>
+  </si>
+  <si>
+    <t>4.1 Arrays</t>
+  </si>
+  <si>
+    <t>Static Arrays</t>
+  </si>
+  <si>
+    <t>// Khai báo: type name[size]</t>
+  </si>
+  <si>
+    <t>int arr[5];              // Uninitialized (garbage values)</t>
+  </si>
+  <si>
+    <t>int nums[5] = {1, 2, 3}; // Partial init: {1, 2, 3, 0, 0}</t>
+  </si>
+  <si>
+    <t>int vals[] = {1, 2, 3};  // Auto size = 3</t>
+  </si>
+  <si>
+    <t>// Truy cập</t>
+  </si>
+  <si>
+    <t>arr[0] = 10;</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; arr[0];</t>
+  </si>
+  <si>
+    <t>// BẪY: Không check bounds!</t>
+  </si>
+  <si>
+    <t>arr[10] = 5;  // Undefined behavior! Có thể crash</t>
+  </si>
+  <si>
+    <t>Dynamic Arrays</t>
+  </si>
+  <si>
+    <t>// Cấp phát runtime</t>
+  </si>
+  <si>
+    <t>int size;</t>
+  </si>
+  <si>
+    <t>cin &gt;&gt; size;</t>
+  </si>
+  <si>
+    <t>int* arr = new int[size];</t>
+  </si>
+  <si>
+    <t>// Sử dụng</t>
+  </si>
+  <si>
+    <t>for (int i = 0; i &lt; size; i++) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    arr[i] = i * 2;</t>
+  </si>
+  <si>
+    <t>// QUAN TRỌNG: Phải delete!</t>
+  </si>
+  <si>
+    <t>delete[] arr;  // Dùng delete[], không phải delete</t>
+  </si>
+  <si>
+    <t>// Modern C++: Dùng vector thay vì dynamic array!</t>
+  </si>
+  <si>
+    <t>vector&lt;int&gt; vec(size);  // Tự động quản lý memory</t>
+  </si>
+  <si>
+    <t>Multi-dimensional Arrays</t>
+  </si>
+  <si>
+    <t>// 2D array</t>
+  </si>
+  <si>
+    <t>int matrix[3][4];  // 3 hàng, 4 cột</t>
+  </si>
+  <si>
+    <t>// Khởi tạo</t>
+  </si>
+  <si>
+    <t>int mat[2][3] = {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    {1, 2, 3},</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    {4, 5, 6}</t>
+  </si>
+  <si>
+    <t>mat[0][0] = 10;</t>
+  </si>
+  <si>
+    <t>// Dynamic 2D array</t>
+  </si>
+  <si>
+    <t>int** arr = new int*[rows];</t>
+  </si>
+  <si>
+    <t>for (int i = 0; i &lt; rows; i++) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    arr[i] = new int[cols];</t>
+  </si>
+  <si>
+    <t>// Delete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    delete[] arr[i];</t>
+  </si>
+  <si>
+    <t>delete[] arr;</t>
+  </si>
+  <si>
+    <t>// Modern: vector&lt;vector&lt;int&gt;&gt;</t>
+  </si>
+  <si>
+    <t>vector&lt;vector&lt;int&gt;&gt; matrix(rows, vector&lt;int&gt;(cols));</t>
+  </si>
+  <si>
+    <t>Array Decay to Pointers</t>
+  </si>
+  <si>
+    <t>int arr[5] = {1, 2, 3, 4, 5};</t>
+  </si>
+  <si>
+    <t>// Array tự động decay thành pointer khi truyền vào function</t>
+  </si>
+  <si>
+    <t>void print(int* ptr, int size) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // ptr là con trỏ, không biết kích thước gốc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // sizeof(ptr) = 8 bytes (kích thước con trỏ), NOT 20!</t>
+  </si>
+  <si>
+    <t>print(arr, 5);  // arr decay thành &amp;arr[0]</t>
+  </si>
+  <si>
+    <t>// BẪY: Mất thông tin kích thước</t>
+  </si>
+  <si>
+    <t>void wrong(int arr[]) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int size = sizeof(arr) / sizeof(arr[0]);  // WRONG!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // sizeof(arr) = sizeof(int*) = 8</t>
+  </si>
+  <si>
+    <t>// Giải pháp: Truyền size hoặc dùng array/vector</t>
+  </si>
+  <si>
+    <t>void correct(int arr[], int size) { }</t>
+  </si>
+  <si>
+    <t>void modern(array&lt;int, 5&gt;&amp; arr) { }  // C++11</t>
+  </si>
+  <si>
+    <t>void best(vector&lt;int&gt;&amp; vec) { }      // Recommended</t>
+  </si>
+  <si>
+    <t>4.2 Strings</t>
+  </si>
+  <si>
+    <t>C-style Strings</t>
+  </si>
+  <si>
+    <t>// Mảng char kết thúc bằng '\0'</t>
+  </si>
+  <si>
+    <t>char str1[] = "Hello";        // {'H','e','l','l','o','\0'}</t>
+  </si>
+  <si>
+    <t>char str2[10] = "Hi";         // Dư chỗ</t>
+  </si>
+  <si>
+    <t>char str3[3] = {'a','b','c'}; // BẪY: Thiếu '\0'!</t>
+  </si>
+  <si>
+    <t>// Functions từ &lt;cstring&gt;</t>
+  </si>
+  <si>
+    <t>strlen(str1);           // 5 (không đếm '\0')</t>
+  </si>
+  <si>
+    <t>strcpy(str2, str1);     // Copy</t>
+  </si>
+  <si>
+    <t>strcat(str2, " World"); // Nối chuỗi</t>
+  </si>
+  <si>
+    <t>strcmp(str1, str2);     // So sánh: 0=equal, &lt;0, &gt;0</t>
+  </si>
+  <si>
+    <t>// BẪY: Buffer overflow</t>
+  </si>
+  <si>
+    <t>char small[5];</t>
+  </si>
+  <si>
+    <t>strcpy(small, "Too long string");  // DANGER! Ghi đè memory</t>
+  </si>
+  <si>
+    <t>std::string Class</t>
+  </si>
+  <si>
+    <t>#include &lt;string&gt;</t>
+  </si>
+  <si>
+    <t>string s1 = "Hello";</t>
+  </si>
+  <si>
+    <t>string s2("World");</t>
+  </si>
+  <si>
+    <t>string s3(5, 'a');      // "aaaaa"</t>
+  </si>
+  <si>
+    <t>// Nối chuỗi</t>
+  </si>
+  <si>
+    <t>string greeting = s1 + " " + s2;  // "Hello World"</t>
+  </si>
+  <si>
+    <t>s1 += "!";             // "Hello!"</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; s1[0];         // 'H'</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; s1.at(0);      // 'H' (check bounds)</t>
+  </si>
+  <si>
+    <t>s1[0] = 'h';           // "hello!"</t>
+  </si>
+  <si>
+    <t>// BẪY: [] không check bounds</t>
+  </si>
+  <si>
+    <t>s1[100] = 'x';         // Undefined behavior!</t>
+  </si>
+  <si>
+    <t>s1.at(100) = 'x';      // Throw exception</t>
+  </si>
+  <si>
+    <t>String Operations</t>
+  </si>
+  <si>
+    <t>string str = "Hello World";</t>
+  </si>
+  <si>
+    <t>// Kích thước</t>
+  </si>
+  <si>
+    <t>str.size();            // 11</t>
+  </si>
+  <si>
+    <t>str.length();          // 11 (giống size())</t>
+  </si>
+  <si>
+    <t>str.empty();           // false</t>
+  </si>
+  <si>
+    <t>// Substring</t>
+  </si>
+  <si>
+    <t>str.substr(0, 5);      // "Hello" (pos, len)</t>
+  </si>
+  <si>
+    <t>str.substr(6);         // "World" (từ pos đến cuối)</t>
+  </si>
+  <si>
+    <t>// Tìm kiếm</t>
+  </si>
+  <si>
+    <t>size_t pos = str.find("World");     // 6</t>
+  </si>
+  <si>
+    <t>if (pos != string::npos) {          // Tìm thấy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; "Found at " &lt;&lt; pos;</t>
+  </si>
+  <si>
+    <t>str.find("xyz");       // string::npos (không tìm thấy)</t>
+  </si>
+  <si>
+    <t>// Replace</t>
+  </si>
+  <si>
+    <t>str.replace(0, 5, "Hi");  // "Hi World" (pos, len, newstr)</t>
+  </si>
+  <si>
+    <t>// Insert &amp; Erase</t>
+  </si>
+  <si>
+    <t>str.insert(2, "!!!");     // "Hi!!! World"</t>
+  </si>
+  <si>
+    <t>str.erase(2, 3);          // "Hi World"</t>
+  </si>
+  <si>
+    <t>// So sánh</t>
+  </si>
+  <si>
+    <t>str.compare("Hi World");  // 0 = equal</t>
+  </si>
+  <si>
+    <t>str == "Hi World";        // true (dễ đọc hơn)</t>
+  </si>
+  <si>
+    <t>String Literals &amp; Raw Strings</t>
+  </si>
+  <si>
+    <t>// Regular string</t>
+  </si>
+  <si>
+    <t>string path = "C:\\Users\\Documents\\file.txt";  // Escape \</t>
+  </si>
+  <si>
+    <t>// Raw string (C++11): R"(content)"</t>
+  </si>
+  <si>
+    <t>string rawPath = R"(C:\Users\Documents\file.txt)";</t>
+  </si>
+  <si>
+    <t>// Multi-line raw string</t>
+  </si>
+  <si>
+    <t>string json = R"(</t>
+  </si>
+  <si>
+    <t>{</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "name": "Alice",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "age": 25</t>
+  </si>
+  <si>
+    <t>)";</t>
+  </si>
+  <si>
+    <t>// Custom delimiter: R"delimiter(content)delimiter"</t>
+  </si>
+  <si>
+    <t>string weird = R"abc(He said: "Raw (string)")abc";</t>
+  </si>
+  <si>
+    <t>CÁC BẪY PHỔ BIẾN &amp; BEST PRACTICES</t>
+  </si>
+  <si>
+    <t>1. Memory Leaks</t>
+  </si>
+  <si>
+    <t>// SAI</t>
+  </si>
+  <si>
+    <t>int* ptr = new int[100];</t>
+  </si>
+  <si>
+    <t>// Quên delete[] → memory leak</t>
+  </si>
+  <si>
+    <t>// ĐÚNG</t>
+  </si>
+  <si>
+    <t>delete[] ptr;</t>
+  </si>
+  <si>
+    <t>// Hoặc dùng smart pointers/vector</t>
+  </si>
+  <si>
+    <t>2. Uninitialized Variables</t>
+  </si>
+  <si>
+    <t>int x;           // Garbage value</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; x;       // Undefined behavior</t>
+  </si>
+  <si>
+    <t>int y = 0;       // Luôn khởi tạo!</t>
+  </si>
+  <si>
+    <t>3. Off-by-One Errors</t>
+  </si>
+  <si>
+    <t>int arr[5];</t>
+  </si>
+  <si>
+    <t>for (int i = 0; i &lt;= 5; i++) {  // SAI! Nên i &lt; 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    arr[i] = 0;  // arr[5] out of bounds</t>
+  </si>
+  <si>
+    <t>4. Integer Overflow</t>
+  </si>
+  <si>
+    <t>int big = 2147483647;</t>
+  </si>
+  <si>
+    <t>big++;  // Overflow thành -2147483648</t>
+  </si>
+  <si>
+    <t>5. Comparing Floats</t>
+  </si>
+  <si>
+    <t>if (0.1 + 0.2 == 0.3) { }  // False do rounding error</t>
+  </si>
+  <si>
+    <t>if (abs((0.1 + 0.2) - 0.3) &lt; 0.00001) { }</t>
+  </si>
+  <si>
+    <t>ỨNG DỤNG PHỔ BIẾN</t>
+  </si>
+  <si>
+    <t>Tóm tắt các điểm quan trọng:</t>
+  </si>
+  <si>
+    <t>Luôn khởi tạo biến, kiểm tra bounds</t>
+  </si>
+  <si>
+    <t>Modern C++ (C++11+): range-based for, auto, lambda</t>
+  </si>
+  <si>
+    <t>Tránh raw pointers khi có thể, dùng smart pointers</t>
+  </si>
+  <si>
+    <r>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Đếm, chỉ số mảng, ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>float</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Đồ họa, game (khi cần tốc độ hơn độ chính xác)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>double</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Tính toán khoa học, tài chính (ưu tiên độ chính xác)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>char</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Ký tự đơn, mã ASCII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>bool</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Cờ trạng thái, điều kiện</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>unsigned</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cho: kích thước, chỉ số mảng khi chắc chắn không âm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>signed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cho: phép toán có thể ra số âm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>static_cast</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Chuyển đổi số, upcasting trong OOP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>dynamic_cast</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Kiểm tra kiểu an toàn khi downcasting</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>const_cast</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Làm việc với legacy code không có const</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>reinterpret_cast</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Lập trình hệ thống, serialization</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>const</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Giá trị không thay đổi nhưng có thể tính runtime</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>constexpr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Hằng số thực sự, cần optimize, dùng cho array size</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Lời khuyên:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>const</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>constexpr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> thay vì </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>#define</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> khi có thể!</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>for</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Duyệt mảng, vector, đếm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>while</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Đọc file đến hết, game loop</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>do-while</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Validate input, menu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Lời khuyên:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tránh C-strings, dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>std::string</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>!</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. Game Development</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Control flow, arrays cho game states</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. System Programming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Pointers, memory management</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Algorithm Contests</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Fast I/O, array manipulation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. Embedded Systems</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Efficient loops, bit operations</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5. Desktop Applications</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: String processing, data structures</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6. Scientific Computing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Arrays, precision types (double)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>7. Web Backends</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: String parsing, JSON handling</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ưu tiên </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>std::string</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>std::vector</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> thay vì C-style</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>const</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>constexpr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> thay vì </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>#define</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Truyền object lớn bằng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>const reference</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Cảnh báo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Tránh trộn signed và unsigned trong phép so sánh!</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3736,8 +5714,52 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3747,6 +5769,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3787,7 +5821,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3812,6 +5846,32 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4147,78 +6207,78 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:DP316"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="16384" width="3" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:58" s="6" customFormat="1" ht="15.75" thickBot="1">
       <c r="A1" s="5" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="2" spans="1:58" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:58" ht="15">
       <c r="A2" s="8" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:58">
       <c r="A3" s="9" t="s">
         <v>346</v>
       </c>
       <c r="B3" s="7"/>
     </row>
-    <row r="4" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:58">
       <c r="A4" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="7"/>
     </row>
-    <row r="5" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:58">
       <c r="A5" s="9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:58">
       <c r="A6" s="9" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="7" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:58">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:58" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:58" ht="15">
       <c r="A8" s="3" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="9" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:58">
       <c r="A9" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:58">
       <c r="A10" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:58">
       <c r="A11" s="4" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="12" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:58">
       <c r="A12" s="4" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="13" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:58" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:58" ht="15" thickBot="1"/>
+    <row r="14" spans="1:58" s="6" customFormat="1" ht="15.75" thickBot="1">
       <c r="A14" s="5" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="15" spans="1:58" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:58" ht="15">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
@@ -4232,7 +6292,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:58" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:58" ht="15">
       <c r="A16" s="3" t="s">
         <v>351</v>
       </c>
@@ -4246,7 +6306,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="17" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:105">
       <c r="A17" s="4" t="s">
         <v>352</v>
       </c>
@@ -4260,7 +6320,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="18" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:105">
       <c r="A18" s="4" t="s">
         <v>353</v>
       </c>
@@ -4274,7 +6334,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="19" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:105">
       <c r="A19" s="4" t="s">
         <v>354</v>
       </c>
@@ -4288,7 +6348,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:105">
       <c r="A20" s="4" t="s">
         <v>355</v>
       </c>
@@ -4300,7 +6360,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:105" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:105" ht="15">
       <c r="A21" s="3"/>
       <c r="S21" s="3" t="s">
         <v>364</v>
@@ -4308,7 +6368,7 @@
       <c r="AM21" s="3"/>
       <c r="BF21" s="3"/>
     </row>
-    <row r="22" spans="1:105" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:105" ht="15">
       <c r="A22" s="3" t="s">
         <v>356</v>
       </c>
@@ -4322,7 +6382,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="23" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:105">
       <c r="A23" s="4" t="s">
         <v>357</v>
       </c>
@@ -4336,7 +6396,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="24" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:105">
       <c r="A24" s="4" t="s">
         <v>358</v>
       </c>
@@ -4350,7 +6410,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="25" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:105">
       <c r="A25" s="4" t="s">
         <v>359</v>
       </c>
@@ -4361,7 +6421,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="26" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:105">
       <c r="AM26" s="4" t="s">
         <v>370</v>
       </c>
@@ -4369,13 +6429,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:105" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:105" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:105" ht="15" thickBot="1"/>
+    <row r="28" spans="1:105" s="6" customFormat="1" ht="15.75" thickBot="1">
       <c r="A28" s="5" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="29" spans="1:105" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:105" s="10" customFormat="1" ht="15">
       <c r="A29" s="1" t="s">
         <v>594</v>
       </c>
@@ -4392,7 +6452,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="30" spans="1:105" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:105" s="10" customFormat="1" ht="15">
       <c r="A30" s="1" t="s">
         <v>595</v>
       </c>
@@ -4412,7 +6472,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="31" spans="1:105" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:105" s="10" customFormat="1" ht="15">
       <c r="A31" s="3" t="s">
         <v>716</v>
       </c>
@@ -4432,7 +6492,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="32" spans="1:105" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:105" s="10" customFormat="1">
       <c r="A32" s="3" t="s">
         <v>717</v>
       </c>
@@ -4452,7 +6512,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="33" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:120" s="10" customFormat="1">
       <c r="A33" s="3" t="s">
         <v>718</v>
       </c>
@@ -4472,7 +6532,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="34" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:120" s="10" customFormat="1">
       <c r="A34" s="3" t="s">
         <v>719</v>
       </c>
@@ -4492,7 +6552,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="35" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:120" s="10" customFormat="1">
       <c r="A35" s="3" t="s">
         <v>596</v>
       </c>
@@ -4510,7 +6570,7 @@
       </c>
       <c r="DA35" s="2"/>
     </row>
-    <row r="36" spans="1:120" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:120" s="10" customFormat="1" ht="15">
       <c r="A36" s="3" t="s">
         <v>597</v>
       </c>
@@ -4528,7 +6588,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="37" spans="1:120" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:120" s="10" customFormat="1" ht="15">
       <c r="A37" s="2"/>
       <c r="W37" s="1" t="s">
         <v>629</v>
@@ -4542,7 +6602,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="38" spans="1:120" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:120" s="10" customFormat="1" ht="15">
       <c r="A38" s="1" t="s">
         <v>598</v>
       </c>
@@ -4560,7 +6620,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="39" spans="1:120" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:120" s="10" customFormat="1" ht="15">
       <c r="A39" s="3" t="s">
         <v>599</v>
       </c>
@@ -4580,7 +6640,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="40" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:120" s="10" customFormat="1">
       <c r="A40" s="3" t="s">
         <v>600</v>
       </c>
@@ -4600,7 +6660,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="41" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:120" s="10" customFormat="1">
       <c r="A41" s="3" t="s">
         <v>601</v>
       </c>
@@ -4618,7 +6678,7 @@
       </c>
       <c r="DA41" s="2"/>
     </row>
-    <row r="42" spans="1:120" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:120" s="10" customFormat="1" ht="15">
       <c r="A42" s="3" t="s">
         <v>602</v>
       </c>
@@ -4636,7 +6696,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="43" spans="1:120" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:120" s="10" customFormat="1" ht="15">
       <c r="A43" s="3" t="s">
         <v>378</v>
       </c>
@@ -4664,7 +6724,7 @@
       <c r="DJ43" s="2"/>
       <c r="DK43" s="2"/>
     </row>
-    <row r="44" spans="1:120" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:120" s="10" customFormat="1" ht="15">
       <c r="A44" s="3" t="s">
         <v>720</v>
       </c>
@@ -4699,7 +6759,7 @@
       <c r="DO44" s="2"/>
       <c r="DP44" s="2"/>
     </row>
-    <row r="45" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:120" s="10" customFormat="1">
       <c r="A45" s="3" t="s">
         <v>721</v>
       </c>
@@ -4732,7 +6792,7 @@
       <c r="DO45" s="2"/>
       <c r="DP45" s="2"/>
     </row>
-    <row r="46" spans="1:120" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:120" s="10" customFormat="1" ht="15">
       <c r="A46" s="2"/>
       <c r="W46" s="3" t="s">
         <v>26</v>
@@ -4765,7 +6825,7 @@
       <c r="DO46" s="2"/>
       <c r="DP46" s="2"/>
     </row>
-    <row r="47" spans="1:120" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:120" s="10" customFormat="1" ht="15">
       <c r="A47" s="1" t="s">
         <v>603</v>
       </c>
@@ -4787,7 +6847,7 @@
       <c r="DO47" s="2"/>
       <c r="DP47" s="2"/>
     </row>
-    <row r="48" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:120" s="10" customFormat="1">
       <c r="A48" s="3" t="s">
         <v>18</v>
       </c>
@@ -4804,7 +6864,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="49" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:86" s="10" customFormat="1">
       <c r="A49" s="3" t="s">
         <v>19</v>
       </c>
@@ -4821,7 +6881,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="50" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:86" s="10" customFormat="1">
       <c r="A50" s="3" t="s">
         <v>604</v>
       </c>
@@ -4834,7 +6894,7 @@
       <c r="BO50" s="2"/>
       <c r="CH50" s="2"/>
     </row>
-    <row r="51" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:86" s="10" customFormat="1" ht="15">
       <c r="A51" s="3" t="s">
         <v>21</v>
       </c>
@@ -4847,7 +6907,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="52" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:86" s="10" customFormat="1" ht="15">
       <c r="A52" s="3" t="s">
         <v>22</v>
       </c>
@@ -4860,7 +6920,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="53" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:86" s="10" customFormat="1" ht="15">
       <c r="A53" s="3" t="s">
         <v>23</v>
       </c>
@@ -4874,7 +6934,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="54" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:86" s="10" customFormat="1">
       <c r="A54" s="3" t="s">
         <v>722</v>
       </c>
@@ -4888,7 +6948,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="55" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:86" s="10" customFormat="1">
       <c r="A55" s="3" t="s">
         <v>605</v>
       </c>
@@ -4902,7 +6962,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="56" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:86" s="10" customFormat="1">
       <c r="A56" s="2"/>
       <c r="W56" s="3" t="s">
         <v>732</v>
@@ -4914,7 +6974,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="57" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:86" s="10" customFormat="1" ht="15">
       <c r="A57" s="1" t="s">
         <v>606</v>
       </c>
@@ -4926,7 +6986,7 @@
       </c>
       <c r="CH57" s="2"/>
     </row>
-    <row r="58" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:86" s="10" customFormat="1" ht="15">
       <c r="A58" s="3" t="s">
         <v>607</v>
       </c>
@@ -4938,7 +6998,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="59" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:86" s="10" customFormat="1">
       <c r="A59" s="3" t="s">
         <v>608</v>
       </c>
@@ -4947,7 +7007,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:86" s="10" customFormat="1" ht="15">
       <c r="A60" s="3" t="s">
         <v>609</v>
       </c>
@@ -4958,7 +7018,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="61" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:86" s="10" customFormat="1">
       <c r="A61" s="3" t="s">
         <v>610</v>
       </c>
@@ -4969,7 +7029,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="62" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:86" s="10" customFormat="1">
       <c r="A62" s="2"/>
       <c r="AT62" s="3" t="s">
         <v>660</v>
@@ -4978,7 +7038,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="63" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:86" s="10" customFormat="1" ht="15">
       <c r="A63" s="1" t="s">
         <v>611</v>
       </c>
@@ -4989,7 +7049,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="64" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:86" s="10" customFormat="1">
       <c r="A64" s="3" t="s">
         <v>612</v>
       </c>
@@ -5000,7 +7060,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="65" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:86" s="10" customFormat="1">
       <c r="A65" s="4" t="s">
         <v>20</v>
       </c>
@@ -5011,7 +7071,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="66" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:86" s="10" customFormat="1">
       <c r="A66" s="4" t="s">
         <v>613</v>
       </c>
@@ -5020,7 +7080,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="67" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:86" s="10" customFormat="1" ht="15">
       <c r="A67" s="4" t="s">
         <v>614</v>
       </c>
@@ -5029,7 +7089,7 @@
       </c>
       <c r="CH67" s="2"/>
     </row>
-    <row r="68" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:86" s="10" customFormat="1" ht="15">
       <c r="A68" s="3" t="s">
         <v>615</v>
       </c>
@@ -5040,7 +7100,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="69" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:86" s="10" customFormat="1">
       <c r="A69" s="4" t="s">
         <v>616</v>
       </c>
@@ -5051,7 +7111,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="70" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:86" s="10" customFormat="1">
       <c r="A70" s="4" t="s">
         <v>617</v>
       </c>
@@ -5062,7 +7122,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="71" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:86" s="10" customFormat="1">
       <c r="A71" s="3" t="s">
         <v>618</v>
       </c>
@@ -5071,7 +7131,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="72" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:86" s="10" customFormat="1">
       <c r="A72" s="3" t="s">
         <v>723</v>
       </c>
@@ -5079,7 +7139,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="73" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:86" s="10" customFormat="1">
       <c r="A73" s="3" t="s">
         <v>724</v>
       </c>
@@ -5087,13 +7147,13 @@
         <v>700</v>
       </c>
     </row>
-    <row r="74" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:86" s="10" customFormat="1">
       <c r="A74" s="2"/>
       <c r="CH74" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="75" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:86" s="10" customFormat="1" ht="15">
       <c r="A75" s="1" t="s">
         <v>619</v>
       </c>
@@ -5101,13 +7161,13 @@
         <v>701</v>
       </c>
     </row>
-    <row r="76" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:86" s="10" customFormat="1">
       <c r="A76" s="3" t="s">
         <v>620</v>
       </c>
       <c r="CH76" s="2"/>
     </row>
-    <row r="77" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:86" s="10" customFormat="1" ht="15">
       <c r="A77" s="3" t="s">
         <v>725</v>
       </c>
@@ -5115,7 +7175,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="78" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:86" s="10" customFormat="1">
       <c r="A78" s="3" t="s">
         <v>621</v>
       </c>
@@ -5123,7 +7183,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="79" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:86" s="10" customFormat="1">
       <c r="A79" s="3" t="s">
         <v>617</v>
       </c>
@@ -5131,7 +7191,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="80" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:86" s="10" customFormat="1">
       <c r="A80" s="3" t="s">
         <v>726</v>
       </c>
@@ -5139,7 +7199,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="81" spans="1:86" s="10" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:86" s="10" customFormat="1" ht="16.5" customHeight="1">
       <c r="A81" s="3" t="s">
         <v>622</v>
       </c>
@@ -5147,16 +7207,16 @@
         <v>705</v>
       </c>
     </row>
-    <row r="82" spans="1:86" s="10" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:86" s="10" customFormat="1" ht="16.5" customHeight="1" thickBot="1">
       <c r="A82" s="3"/>
       <c r="CH82" s="3"/>
     </row>
-    <row r="83" spans="1:86" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:86" s="6" customFormat="1" ht="15.75" thickBot="1">
       <c r="A83" s="5" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="84" spans="1:86" ht="15" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:86" ht="15">
       <c r="A84" s="1" t="s">
         <v>29</v>
       </c>
@@ -5167,7 +7227,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="85" spans="1:86" ht="15" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:86" ht="15">
       <c r="A85" s="3" t="s">
         <v>382</v>
       </c>
@@ -5178,7 +7238,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="86" spans="1:86" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:86">
       <c r="A86" s="4" t="s">
         <v>30</v>
       </c>
@@ -5189,7 +7249,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="87" spans="1:86" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:86">
       <c r="A87" s="4" t="s">
         <v>383</v>
       </c>
@@ -5200,7 +7260,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="88" spans="1:86" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:86">
       <c r="A88" s="4" t="s">
         <v>384</v>
       </c>
@@ -5211,7 +7271,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="89" spans="1:86" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:86">
       <c r="A89" s="4" t="s">
         <v>385</v>
       </c>
@@ -5222,19 +7282,19 @@
         <v>44</v>
       </c>
     </row>
-    <row r="90" spans="1:86" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:86">
       <c r="A90" s="4" t="s">
         <v>31</v>
       </c>
       <c r="S90" s="3"/>
     </row>
-    <row r="91" spans="1:86" ht="15" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:86" ht="15">
       <c r="A91" s="3"/>
       <c r="S91" s="3" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="92" spans="1:86" ht="15" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:86" ht="15">
       <c r="A92" s="3" t="s">
         <v>386</v>
       </c>
@@ -5242,7 +7302,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="93" spans="1:86" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:86">
       <c r="A93" s="4" t="s">
         <v>387</v>
       </c>
@@ -5250,7 +7310,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="94" spans="1:86" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:86">
       <c r="A94" s="4" t="s">
         <v>12</v>
       </c>
@@ -5258,7 +7318,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="95" spans="1:86" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:86">
       <c r="A95" s="4" t="s">
         <v>388</v>
       </c>
@@ -5266,7 +7326,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="96" spans="1:86" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:86">
       <c r="A96" s="4" t="s">
         <v>389</v>
       </c>
@@ -5274,41 +7334,41 @@
         <v>39</v>
       </c>
     </row>
-    <row r="97" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:37">
       <c r="A97" s="3"/>
     </row>
-    <row r="98" spans="1:37" ht="15" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:37" ht="15">
       <c r="A98" s="3" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="99" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:37">
       <c r="A99" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="100" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:37">
       <c r="A100" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="101" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:37">
       <c r="A101" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="102" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:37">
       <c r="A102" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="103" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="1:37" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:37" ht="15" thickBot="1"/>
+    <row r="104" spans="1:37" s="6" customFormat="1" ht="15.75" thickBot="1">
       <c r="A104" s="5" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="105" spans="1:37" ht="15" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:37" ht="15">
       <c r="A105" s="1" t="s">
         <v>45</v>
       </c>
@@ -5319,7 +7379,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="106" spans="1:37" ht="15" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:37" ht="15">
       <c r="A106" s="3" t="s">
         <v>400</v>
       </c>
@@ -5330,7 +7390,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="107" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:37">
       <c r="A107" s="4" t="s">
         <v>46</v>
       </c>
@@ -5341,7 +7401,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="108" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:37">
       <c r="A108" s="4" t="s">
         <v>47</v>
       </c>
@@ -5352,7 +7412,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="109" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:37">
       <c r="A109" s="4" t="s">
         <v>48</v>
       </c>
@@ -5363,7 +7423,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="110" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:37">
       <c r="A110" s="4" t="s">
         <v>49</v>
       </c>
@@ -5374,12 +7434,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="111" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:37">
       <c r="A111" s="3"/>
       <c r="S111" s="3"/>
       <c r="AK111" s="3"/>
     </row>
-    <row r="112" spans="1:37" ht="15" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:37" ht="15">
       <c r="A112" s="3" t="s">
         <v>401</v>
       </c>
@@ -5390,7 +7450,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="113" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:51">
       <c r="A113" s="4" t="s">
         <v>50</v>
       </c>
@@ -5401,7 +7461,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="114" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:51">
       <c r="A114" s="4" t="s">
         <v>27</v>
       </c>
@@ -5412,7 +7472,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="115" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:51">
       <c r="A115" s="4" t="s">
         <v>51</v>
       </c>
@@ -5423,7 +7483,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="116" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:51">
       <c r="A116" s="4" t="s">
         <v>52</v>
       </c>
@@ -5431,41 +7491,41 @@
         <v>409</v>
       </c>
     </row>
-    <row r="117" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:51">
       <c r="A117" s="3"/>
     </row>
-    <row r="118" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:51" ht="15">
       <c r="A118" s="3" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="119" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:51">
       <c r="A119" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="120" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:51">
       <c r="A120" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="121" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:51">
       <c r="A121" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="122" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:51">
       <c r="A122" s="4" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="123" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="1:51" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:51" ht="15" thickBot="1"/>
+    <row r="124" spans="1:51" s="6" customFormat="1" ht="15.75" thickBot="1">
       <c r="A124" s="5" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="125" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:51" ht="15">
       <c r="A125" s="1" t="s">
         <v>65</v>
       </c>
@@ -5479,7 +7539,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="126" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:51" ht="15">
       <c r="A126" s="3" t="s">
         <v>416</v>
       </c>
@@ -5493,7 +7553,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="127" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:51">
       <c r="A127" s="4" t="s">
         <v>417</v>
       </c>
@@ -5507,7 +7567,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="128" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:51">
       <c r="A128" s="4" t="s">
         <v>418</v>
       </c>
@@ -5521,7 +7581,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="129" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:51">
       <c r="A129" s="4" t="s">
         <v>419</v>
       </c>
@@ -5535,7 +7595,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="130" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:51">
       <c r="A130" s="4" t="s">
         <v>420</v>
       </c>
@@ -5549,7 +7609,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="131" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:51">
       <c r="A131" s="4" t="s">
         <v>421</v>
       </c>
@@ -5557,7 +7617,7 @@
       <c r="AJ131" s="3"/>
       <c r="AY131" s="3"/>
     </row>
-    <row r="132" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:51" ht="15">
       <c r="A132" s="3"/>
       <c r="U132" s="3" t="s">
         <v>432</v>
@@ -5569,7 +7629,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="133" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:51" ht="15">
       <c r="A133" s="3" t="s">
         <v>422</v>
       </c>
@@ -5583,7 +7643,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="134" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:51">
       <c r="A134" s="4" t="s">
         <v>423</v>
       </c>
@@ -5597,7 +7657,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="135" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:51">
       <c r="A135" s="4" t="s">
         <v>424</v>
       </c>
@@ -5611,7 +7671,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="136" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:51">
       <c r="A136" s="4" t="s">
         <v>425</v>
       </c>
@@ -5625,19 +7685,19 @@
         <v>456</v>
       </c>
     </row>
-    <row r="137" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:51">
       <c r="A137" s="4" t="s">
         <v>426</v>
       </c>
       <c r="AJ137" s="3"/>
     </row>
-    <row r="138" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:51" ht="15">
       <c r="A138" s="3"/>
       <c r="AJ138" s="3" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="139" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:51" ht="15">
       <c r="A139" s="3" t="s">
         <v>427</v>
       </c>
@@ -5645,7 +7705,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="140" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:51">
       <c r="A140" s="4" t="s">
         <v>428</v>
       </c>
@@ -5653,7 +7713,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="141" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:51">
       <c r="A141" s="4" t="s">
         <v>429</v>
       </c>
@@ -5661,7 +7721,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="142" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:51">
       <c r="A142" s="4" t="s">
         <v>430</v>
       </c>
@@ -5669,13 +7729,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="143" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="1:51" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:51" ht="15" thickBot="1"/>
+    <row r="144" spans="1:51" s="6" customFormat="1" ht="15.75" thickBot="1">
       <c r="A144" s="5" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="145" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:48" ht="15">
       <c r="A145" s="1" t="s">
         <v>78</v>
       </c>
@@ -5689,7 +7749,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="146" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:48" ht="15">
       <c r="A146" s="3" t="s">
         <v>457</v>
       </c>
@@ -5703,7 +7763,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="147" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:48">
       <c r="A147" s="4" t="s">
         <v>458</v>
       </c>
@@ -5717,7 +7777,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="148" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:48">
       <c r="A148" s="4" t="s">
         <v>79</v>
       </c>
@@ -5731,7 +7791,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="149" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:48">
       <c r="A149" s="4" t="s">
         <v>459</v>
       </c>
@@ -5745,7 +7805,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="150" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:48">
       <c r="A150" s="4" t="s">
         <v>80</v>
       </c>
@@ -5759,12 +7819,12 @@
         <v>482</v>
       </c>
     </row>
-    <row r="151" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:48">
       <c r="A151" s="3"/>
       <c r="R151" s="3"/>
       <c r="AG151" s="3"/>
     </row>
-    <row r="152" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:48" ht="15">
       <c r="A152" s="3" t="s">
         <v>460</v>
       </c>
@@ -5775,7 +7835,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="153" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:48">
       <c r="A153" s="4" t="s">
         <v>461</v>
       </c>
@@ -5786,7 +7846,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="154" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:48">
       <c r="A154" s="4" t="s">
         <v>81</v>
       </c>
@@ -5797,7 +7857,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="155" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:48">
       <c r="A155" s="4" t="s">
         <v>82</v>
       </c>
@@ -5808,40 +7868,40 @@
         <v>91</v>
       </c>
     </row>
-    <row r="156" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:48">
       <c r="R156" s="4" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="157" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:48">
       <c r="R157" s="3"/>
     </row>
-    <row r="158" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:48" ht="15">
       <c r="R158" s="3" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="159" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:48">
       <c r="R159" s="4" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="160" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:48">
       <c r="R160" s="4" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="161" spans="1:45" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:45" ht="15" customHeight="1" thickBot="1">
       <c r="R161" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="162" spans="1:45" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:45" s="6" customFormat="1" ht="15.75" thickBot="1">
       <c r="A162" s="5" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="163" spans="1:45" ht="15" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:45" ht="15">
       <c r="A163" s="1" t="s">
         <v>93</v>
       </c>
@@ -5855,7 +7915,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="164" spans="1:45" ht="15" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:45" ht="15">
       <c r="A164" s="3" t="s">
         <v>483</v>
       </c>
@@ -5869,7 +7929,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="165" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:45">
       <c r="A165" s="4" t="s">
         <v>484</v>
       </c>
@@ -5883,7 +7943,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="166" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:45">
       <c r="A166" s="4" t="s">
         <v>485</v>
       </c>
@@ -5897,7 +7957,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="167" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:45">
       <c r="A167" s="4" t="s">
         <v>94</v>
       </c>
@@ -5907,7 +7967,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="168" spans="1:45" ht="15" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:45" ht="15">
       <c r="A168" s="3"/>
       <c r="S168" s="3" t="s">
         <v>494</v>
@@ -5917,7 +7977,7 @@
       </c>
       <c r="AS168" s="3"/>
     </row>
-    <row r="169" spans="1:45" ht="15" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:45" ht="15">
       <c r="A169" s="3" t="s">
         <v>486</v>
       </c>
@@ -5931,7 +7991,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="170" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:45">
       <c r="A170" s="4" t="s">
         <v>72</v>
       </c>
@@ -5945,7 +8005,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="171" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:45">
       <c r="A171" s="4" t="s">
         <v>95</v>
       </c>
@@ -5956,11 +8016,11 @@
         <v>111</v>
       </c>
     </row>
-    <row r="172" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:45">
       <c r="A172" s="3"/>
       <c r="AF172" s="3"/>
     </row>
-    <row r="173" spans="1:45" ht="15" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:45" ht="15">
       <c r="A173" s="3" t="s">
         <v>487</v>
       </c>
@@ -5968,7 +8028,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="174" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:45">
       <c r="A174" s="4" t="s">
         <v>96</v>
       </c>
@@ -5976,7 +8036,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="175" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:45">
       <c r="A175" s="4" t="s">
         <v>488</v>
       </c>
@@ -5984,51 +8044,51 @@
         <v>106</v>
       </c>
     </row>
-    <row r="176" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:45">
       <c r="A176" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="177" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:33">
       <c r="A177" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="178" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:33">
       <c r="A178" s="3"/>
     </row>
-    <row r="179" spans="1:33" ht="15" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:33" ht="15">
       <c r="A179" s="3" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="180" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:33">
       <c r="A180" s="4" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="181" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:33">
       <c r="A181" s="4" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="182" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:33">
       <c r="A182" s="4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="183" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:33">
       <c r="A183" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="184" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="1:33" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:33" ht="15" thickBot="1"/>
+    <row r="185" spans="1:33" s="6" customFormat="1" ht="15.75" thickBot="1">
       <c r="A185" s="5" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="186" spans="1:33" ht="15" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:33" ht="15">
       <c r="A186" s="1" t="s">
         <v>112</v>
       </c>
@@ -6039,7 +8099,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="187" spans="1:33" ht="15" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:33" ht="15">
       <c r="A187" s="3" t="s">
         <v>507</v>
       </c>
@@ -6050,7 +8110,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="188" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:33">
       <c r="A188" s="4" t="s">
         <v>113</v>
       </c>
@@ -6061,7 +8121,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="189" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:33">
       <c r="A189" s="4" t="s">
         <v>114</v>
       </c>
@@ -6072,7 +8132,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="190" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:33">
       <c r="A190" s="4" t="s">
         <v>115</v>
       </c>
@@ -6083,12 +8143,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="191" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:33">
       <c r="A191" s="3"/>
       <c r="R191" s="3"/>
       <c r="AG191" s="3"/>
     </row>
-    <row r="192" spans="1:33" ht="15" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:33" ht="15">
       <c r="A192" s="3" t="s">
         <v>508</v>
       </c>
@@ -6099,7 +8159,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="193" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:48">
       <c r="A193" s="4" t="s">
         <v>116</v>
       </c>
@@ -6110,7 +8170,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="194" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:48">
       <c r="A194" s="4" t="s">
         <v>117</v>
       </c>
@@ -6121,7 +8181,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="195" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:48">
       <c r="A195" s="4" t="s">
         <v>118</v>
       </c>
@@ -6132,12 +8192,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="196" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:48">
       <c r="A196" s="3"/>
       <c r="R196" s="3"/>
       <c r="AG196" s="3"/>
     </row>
-    <row r="197" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:48" ht="15">
       <c r="A197" s="3" t="s">
         <v>509</v>
       </c>
@@ -6148,7 +8208,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="198" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:48">
       <c r="A198" s="4" t="s">
         <v>119</v>
       </c>
@@ -6159,7 +8219,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="199" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:48">
       <c r="A199" s="4" t="s">
         <v>120</v>
       </c>
@@ -6170,7 +8230,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="200" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:48">
       <c r="A200" s="4" t="s">
         <v>121</v>
       </c>
@@ -6181,13 +8241,13 @@
         <v>141</v>
       </c>
     </row>
-    <row r="201" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="1:48" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:48" ht="15" thickBot="1"/>
+    <row r="202" spans="1:48" s="6" customFormat="1" ht="15.75" thickBot="1">
       <c r="A202" s="5" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="203" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:48" ht="15">
       <c r="A203" s="1" t="s">
         <v>142</v>
       </c>
@@ -6201,7 +8261,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="204" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:48" ht="15">
       <c r="A204" s="3" t="s">
         <v>516</v>
       </c>
@@ -6215,7 +8275,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="205" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:48">
       <c r="A205" s="4" t="s">
         <v>143</v>
       </c>
@@ -6229,7 +8289,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="206" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:48">
       <c r="A206" s="4" t="s">
         <v>144</v>
       </c>
@@ -6243,7 +8303,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="207" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:48">
       <c r="A207" s="4" t="s">
         <v>145</v>
       </c>
@@ -6257,7 +8317,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="208" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:48">
       <c r="A208" s="4" t="s">
         <v>146</v>
       </c>
@@ -6271,13 +8331,13 @@
         <v>172</v>
       </c>
     </row>
-    <row r="209" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:48">
       <c r="A209" s="3"/>
       <c r="R209" s="3"/>
       <c r="AG209" s="3"/>
       <c r="AV209" s="3"/>
     </row>
-    <row r="210" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:48" ht="15">
       <c r="A210" s="3" t="s">
         <v>517</v>
       </c>
@@ -6291,7 +8351,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="211" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:48">
       <c r="A211" s="4" t="s">
         <v>147</v>
       </c>
@@ -6305,7 +8365,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="212" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:48">
       <c r="A212" s="4" t="s">
         <v>148</v>
       </c>
@@ -6319,7 +8379,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="213" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:48">
       <c r="A213" s="4" t="s">
         <v>149</v>
       </c>
@@ -6333,7 +8393,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="214" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:48">
       <c r="A214" s="4" t="s">
         <v>150</v>
       </c>
@@ -6347,40 +8407,40 @@
         <v>176</v>
       </c>
     </row>
-    <row r="215" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:48">
       <c r="R215" s="3"/>
     </row>
-    <row r="216" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:48" ht="15">
       <c r="R216" s="3" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="217" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:48">
       <c r="R217" s="4" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="218" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:48">
       <c r="R218" s="4" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="219" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:48">
       <c r="R219" s="4" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="220" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:48" ht="15" thickBot="1">
       <c r="R220" s="4" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="221" spans="1:48" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:48" s="6" customFormat="1" ht="15.75" thickBot="1">
       <c r="A221" s="5" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="222" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:48" ht="15">
       <c r="A222" s="1" t="s">
         <v>177</v>
       </c>
@@ -6394,7 +8454,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="223" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:48" ht="15">
       <c r="A223" s="3" t="s">
         <v>530</v>
       </c>
@@ -6408,7 +8468,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="224" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:48">
       <c r="A224" s="4" t="s">
         <v>531</v>
       </c>
@@ -6422,7 +8482,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="225" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:48">
       <c r="A225" s="4" t="s">
         <v>532</v>
       </c>
@@ -6436,7 +8496,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="226" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:48">
       <c r="A226" s="4" t="s">
         <v>178</v>
       </c>
@@ -6450,7 +8510,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="227" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:48">
       <c r="A227" s="4" t="s">
         <v>179</v>
       </c>
@@ -6464,13 +8524,13 @@
         <v>201</v>
       </c>
     </row>
-    <row r="228" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:48">
       <c r="A228" s="3"/>
       <c r="R228" s="3"/>
       <c r="AE228" s="3"/>
       <c r="AV228" s="3"/>
     </row>
-    <row r="229" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:48" ht="15">
       <c r="A229" s="3" t="s">
         <v>533</v>
       </c>
@@ -6484,7 +8544,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="230" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:48">
       <c r="A230" s="4" t="s">
         <v>534</v>
       </c>
@@ -6498,7 +8558,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="231" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:48">
       <c r="A231" s="4" t="s">
         <v>180</v>
       </c>
@@ -6512,7 +8572,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="232" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:48">
       <c r="A232" s="4" t="s">
         <v>181</v>
       </c>
@@ -6526,7 +8586,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="233" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:48">
       <c r="A233" s="4" t="s">
         <v>182</v>
       </c>
@@ -6540,18 +8600,18 @@
         <v>205</v>
       </c>
     </row>
-    <row r="234" spans="1:48" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:48" ht="13.5" customHeight="1">
       <c r="R234" s="4" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="235" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="236" spans="1:48" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:48" ht="15" thickBot="1"/>
+    <row r="236" spans="1:48" s="6" customFormat="1" ht="15.75" thickBot="1">
       <c r="A236" s="5" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="237" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:48" ht="15">
       <c r="A237" s="1" t="s">
         <v>206</v>
       </c>
@@ -6562,7 +8622,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="238" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:48" ht="15">
       <c r="A238" s="3" t="s">
         <v>546</v>
       </c>
@@ -6573,7 +8633,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="239" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:48">
       <c r="A239" s="4" t="s">
         <v>207</v>
       </c>
@@ -6584,7 +8644,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="240" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:48">
       <c r="A240" s="4" t="s">
         <v>208</v>
       </c>
@@ -6595,7 +8655,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="241" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:33">
       <c r="A241" s="4" t="s">
         <v>209</v>
       </c>
@@ -6606,12 +8666,12 @@
         <v>235</v>
       </c>
     </row>
-    <row r="242" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:33">
       <c r="A242" s="3"/>
       <c r="R242" s="3"/>
       <c r="AG242" s="3"/>
     </row>
-    <row r="243" spans="1:33" ht="15" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:33" ht="15">
       <c r="A243" s="3" t="s">
         <v>547</v>
       </c>
@@ -6622,7 +8682,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="244" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:33">
       <c r="A244" s="4" t="s">
         <v>210</v>
       </c>
@@ -6633,7 +8693,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="245" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:33">
       <c r="A245" s="4" t="s">
         <v>211</v>
       </c>
@@ -6644,7 +8704,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="246" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:33">
       <c r="A246" s="4" t="s">
         <v>212</v>
       </c>
@@ -6655,14 +8715,14 @@
         <v>238</v>
       </c>
     </row>
-    <row r="247" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:33">
       <c r="A247" s="3"/>
       <c r="R247" s="3"/>
       <c r="AG247" s="4" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="248" spans="1:33" ht="15" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:33" ht="15">
       <c r="A248" s="3" t="s">
         <v>548</v>
       </c>
@@ -6671,7 +8731,7 @@
       </c>
       <c r="AG248" s="3"/>
     </row>
-    <row r="249" spans="1:33" ht="15" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:33" ht="15">
       <c r="A249" s="4" t="s">
         <v>213</v>
       </c>
@@ -6682,7 +8742,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="250" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:33">
       <c r="A250" s="4" t="s">
         <v>214</v>
       </c>
@@ -6693,7 +8753,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="251" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:33">
       <c r="A251" s="4" t="s">
         <v>215</v>
       </c>
@@ -6704,62 +8764,62 @@
         <v>241</v>
       </c>
     </row>
-    <row r="252" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:33">
       <c r="A252" s="3"/>
       <c r="AG252" s="4" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="253" spans="1:33" ht="15" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:33" ht="15">
       <c r="A253" s="3" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="254" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:33">
       <c r="A254" s="4" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="255" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:33">
       <c r="A255" s="4" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="256" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:33">
       <c r="A256" s="4" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="257" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:49">
       <c r="A257" s="3"/>
     </row>
-    <row r="258" spans="1:49" ht="15" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:49" ht="15">
       <c r="A258" s="3" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="259" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:49">
       <c r="A259" s="4" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="260" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:49">
       <c r="A260" s="4" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="261" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:49">
       <c r="A261" s="4" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="262" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="263" spans="1:49" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:49" ht="15" thickBot="1"/>
+    <row r="263" spans="1:49" s="6" customFormat="1" ht="15.75" thickBot="1">
       <c r="A263" s="5" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="264" spans="1:49" ht="15" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:49" ht="15">
       <c r="A264" s="1" t="s">
         <v>243</v>
       </c>
@@ -6773,7 +8833,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="265" spans="1:49" ht="15" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:49" ht="15">
       <c r="A265" s="3" t="s">
         <v>557</v>
       </c>
@@ -6787,7 +8847,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="266" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:49">
       <c r="A266" s="4" t="s">
         <v>244</v>
       </c>
@@ -6801,7 +8861,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="267" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:49">
       <c r="A267" s="4" t="s">
         <v>245</v>
       </c>
@@ -6815,7 +8875,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="268" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:49">
       <c r="A268" s="4" t="s">
         <v>246</v>
       </c>
@@ -6829,7 +8889,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="269" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:49">
       <c r="A269" s="4" t="s">
         <v>247</v>
       </c>
@@ -6841,7 +8901,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="270" spans="1:49" ht="15" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:49" ht="15">
       <c r="A270" s="3"/>
       <c r="R270" s="3"/>
       <c r="AF270" s="3" t="s">
@@ -6849,7 +8909,7 @@
       </c>
       <c r="AW270" s="3"/>
     </row>
-    <row r="271" spans="1:49" ht="15" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:49" ht="15">
       <c r="A271" s="3" t="s">
         <v>558</v>
       </c>
@@ -6863,7 +8923,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="272" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:49">
       <c r="A272" s="4" t="s">
         <v>248</v>
       </c>
@@ -6877,7 +8937,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="273" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:49">
       <c r="A273" s="4" t="s">
         <v>249</v>
       </c>
@@ -6891,7 +8951,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="274" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:49">
       <c r="A274" s="4" t="s">
         <v>250</v>
       </c>
@@ -6902,7 +8962,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="275" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:49">
       <c r="A275" s="4" t="s">
         <v>251</v>
       </c>
@@ -6913,74 +8973,74 @@
         <v>276</v>
       </c>
     </row>
-    <row r="276" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:49">
       <c r="AW276" s="4" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="277" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:49">
       <c r="AW277" s="3"/>
     </row>
-    <row r="278" spans="1:49" ht="15" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:49" ht="15">
       <c r="AW278" s="3" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="279" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:49">
       <c r="AW279" s="4" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="280" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:49">
       <c r="AW280" s="4" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="281" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:49">
       <c r="AW281" s="4" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="282" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:49">
       <c r="AW282" s="4" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="283" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:49">
       <c r="AW283" s="3"/>
     </row>
-    <row r="284" spans="1:49" ht="15" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:49" ht="15">
       <c r="AW284" s="3" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="285" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:49">
       <c r="AW285" s="4" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="286" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:49">
       <c r="AW286" s="4" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="287" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:49">
       <c r="AW287" s="4" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="288" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:49">
       <c r="AW288" s="4" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="289" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="290" spans="1:31" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:31" ht="15" thickBot="1"/>
+    <row r="290" spans="1:31" s="6" customFormat="1" ht="15.75" thickBot="1">
       <c r="A290" s="5" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="291" spans="1:31" ht="15" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:31" ht="15">
       <c r="A291" s="1" t="s">
         <v>286</v>
       </c>
@@ -6991,7 +9051,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="292" spans="1:31" ht="15" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:31" ht="15">
       <c r="A292" s="3" t="s">
         <v>567</v>
       </c>
@@ -7002,7 +9062,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="293" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:31">
       <c r="A293" s="4" t="s">
         <v>287</v>
       </c>
@@ -7013,7 +9073,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="294" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:31">
       <c r="A294" s="4" t="s">
         <v>288</v>
       </c>
@@ -7024,7 +9084,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="295" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:31">
       <c r="A295" s="4" t="s">
         <v>289</v>
       </c>
@@ -7035,7 +9095,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="296" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:31">
       <c r="A296" s="4" t="s">
         <v>290</v>
       </c>
@@ -7046,12 +9106,12 @@
         <v>307</v>
       </c>
     </row>
-    <row r="297" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:31">
       <c r="A297" s="3"/>
       <c r="Q297" s="3"/>
       <c r="AE297" s="3"/>
     </row>
-    <row r="298" spans="1:31" ht="15" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:31" ht="15">
       <c r="A298" s="3" t="s">
         <v>568</v>
       </c>
@@ -7062,7 +9122,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="299" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:31">
       <c r="A299" s="4" t="s">
         <v>291</v>
       </c>
@@ -7073,7 +9133,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="300" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:31">
       <c r="A300" s="4" t="s">
         <v>292</v>
       </c>
@@ -7084,7 +9144,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="301" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:31">
       <c r="A301" s="4" t="s">
         <v>293</v>
       </c>
@@ -7095,7 +9155,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="302" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:31">
       <c r="A302" s="4" t="s">
         <v>294</v>
       </c>
@@ -7106,13 +9166,13 @@
         <v>311</v>
       </c>
     </row>
-    <row r="303" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="304" spans="1:31" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:31" ht="15" thickBot="1"/>
+    <row r="304" spans="1:31" s="6" customFormat="1" ht="15.75" thickBot="1">
       <c r="A304" s="5" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="305" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:48" ht="15">
       <c r="A305" s="1" t="s">
         <v>312</v>
       </c>
@@ -7126,7 +9186,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="306" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:48" ht="15">
       <c r="A306" s="3" t="s">
         <v>573</v>
       </c>
@@ -7140,7 +9200,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="307" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:48">
       <c r="A307" s="4" t="s">
         <v>313</v>
       </c>
@@ -7154,7 +9214,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="308" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:48">
       <c r="A308" s="4" t="s">
         <v>314</v>
       </c>
@@ -7168,7 +9228,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="309" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:48">
       <c r="A309" s="4" t="s">
         <v>315</v>
       </c>
@@ -7182,7 +9242,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="310" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:48">
       <c r="A310" s="4" t="s">
         <v>316</v>
       </c>
@@ -7196,7 +9256,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="311" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:48">
       <c r="A311" s="3"/>
       <c r="P311" s="3"/>
       <c r="AE311" s="3"/>
@@ -7204,7 +9264,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="312" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:48" ht="15">
       <c r="A312" s="3" t="s">
         <v>574</v>
       </c>
@@ -7215,7 +9275,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="313" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:48">
       <c r="A313" s="4" t="s">
         <v>317</v>
       </c>
@@ -7226,7 +9286,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="314" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:48">
       <c r="A314" s="4" t="s">
         <v>318</v>
       </c>
@@ -7237,7 +9297,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="315" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:48">
       <c r="A315" s="4" t="s">
         <v>319</v>
       </c>
@@ -7248,7 +9308,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="316" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:48">
       <c r="A316" s="4" t="s">
         <v>320</v>
       </c>
@@ -7262,4 +9322,3002 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:R735"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="16384" width="3" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="21" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A1" s="20" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15">
+      <c r="A2" s="22" t="s">
+        <v>773</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+    </row>
+    <row r="3" spans="1:6" ht="15">
+      <c r="A3" s="12" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="B4" s="13" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5" s="13" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6" s="13" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7" s="13" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8" s="13" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9" s="13" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15">
+      <c r="A11" s="16" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12" s="13" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13" s="13" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" s="13" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="B15" s="13" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="B16" s="13" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="15">
+      <c r="A18" s="12" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="B19" s="13" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="B20" s="13" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="B21" s="14"/>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="B22" s="17" t="s">
+        <v>785</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="18"/>
+      <c r="R22" s="18"/>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="B23" s="17" t="s">
+        <v>786</v>
+      </c>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="18"/>
+      <c r="Q23" s="18"/>
+      <c r="R23" s="18"/>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="B24" s="17" t="s">
+        <v>787</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="18"/>
+      <c r="Q24" s="18"/>
+      <c r="R24" s="18"/>
+    </row>
+    <row r="26" spans="1:18" ht="15">
+      <c r="A26" s="16" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="B27" s="14" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="B28" s="14" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="15">
+      <c r="A29" s="19" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="B30" s="13" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="B31" s="13" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="B32" s="13" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="B33" s="13" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="B34" s="13" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15">
+      <c r="A36" s="12" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="B37" s="13" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="B38" s="13" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="B39" s="13" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="14"/>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="B41" s="13" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="B42" s="13" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="B43" s="13" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="B44" s="13" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="B45" s="13" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="14"/>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="B47" s="13" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="B48" s="13" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="B49" s="13" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="B50" s="14"/>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="B51" s="13" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="B52" s="13" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="B53" s="13" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="15">
+      <c r="A55" s="16" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="14"/>
+      <c r="B56" s="13" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="B57" s="13" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="B58" s="13" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="B59" s="13" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="15">
+      <c r="A62" s="12" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="B63" s="13" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="B64" s="13" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="B65" s="13" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="B66" s="14"/>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="B67" s="13" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="B68" s="13" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="B69" s="13" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="B70" s="14"/>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="B71" s="13" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="B72" s="13" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="B73" s="13" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="15">
+      <c r="A78" s="12" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="15">
+      <c r="A80" s="12" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="13" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="13" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="13" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="14"/>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="13" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="13" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="13" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="14"/>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="13" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="13" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="13" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" ht="15">
+      <c r="A94" s="16" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="14"/>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="13" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="13" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" ht="15">
+      <c r="A99" s="12" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="13" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="13" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="13" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="14"/>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="13" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="13" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="14"/>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="13" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="13" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="13" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="14"/>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="13" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="13" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="13" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" ht="15">
+      <c r="A116" s="16" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" ht="15">
+      <c r="A118" s="12" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="13" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="13" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="13" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="13" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="14"/>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="13" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="13" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="14"/>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="13" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="13" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="13" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="13" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="13" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" ht="15">
+      <c r="A136" s="12" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" ht="15">
+      <c r="A138" s="12" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" ht="15">
+      <c r="A140" s="12" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="13" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="13" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="13" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="14"/>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="13" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="13" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="13" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="13" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="14"/>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="13" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="13" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="13" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="13" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="13" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="13" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" ht="15">
+      <c r="A160" s="16" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="14"/>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" s="13" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="13" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="13" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" ht="15">
+      <c r="A166" s="12" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="13" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="14"/>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" s="13" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="13" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" s="13" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="14"/>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" s="13" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="13" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="13" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" s="14"/>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" s="13" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" s="13" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" s="13" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" s="14"/>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" s="13" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" s="13" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" s="13" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" ht="15">
+      <c r="A190" s="16" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" s="13" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" s="13" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" s="13" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" s="14"/>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" s="13" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" s="13" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" s="13" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" ht="15">
+      <c r="A202" s="12" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" s="13" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" s="13" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" s="13" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" s="13" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" s="14"/>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" s="13" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" s="13" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" s="13" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" s="13" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" s="14"/>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" s="13" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" s="13" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" s="13" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" s="13" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" s="13" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" s="13" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" ht="15">
+      <c r="A226" s="12" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" ht="15">
+      <c r="A228" s="12" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" s="13" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" s="13" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="13" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" s="13" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" s="13" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" s="13" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" s="13" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" s="13" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" s="14"/>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" s="13" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" s="13" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" s="13" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" s="13" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" s="13" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" s="13" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" s="13" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" s="13" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248" s="13" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" s="13" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250" s="13" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" s="13" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" ht="15">
+      <c r="A254" s="16" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256" s="13" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" s="13" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258" s="13" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259" s="13" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260" s="13" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261" s="13" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" ht="15">
+      <c r="A264" s="12" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266" s="13" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267" s="13" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268" s="13" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269" s="14"/>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270" s="13" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271" s="13" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272" s="13" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273" s="13" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274" s="13" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" ht="15">
+      <c r="A276" s="12" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278" s="13" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279" s="13" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280" s="13" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282" s="14"/>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283" s="13" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284" s="13" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285" s="13" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287" s="14"/>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288" s="13" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289" s="13" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1">
+      <c r="A290" s="13" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1">
+      <c r="A291" s="13" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1">
+      <c r="A292" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" ht="15">
+      <c r="A296" s="12" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" ht="15">
+      <c r="A298" s="12" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" ht="15">
+      <c r="A300" s="12" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1">
+      <c r="A302" s="13" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1">
+      <c r="A303" s="13" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1">
+      <c r="A304" s="14"/>
+    </row>
+    <row r="305" spans="1:1">
+      <c r="A305" s="13" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1">
+      <c r="A306" s="13" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1">
+      <c r="A307" s="13" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1">
+      <c r="A308" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1">
+      <c r="A309" s="14"/>
+    </row>
+    <row r="310" spans="1:1">
+      <c r="A310" s="13" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1">
+      <c r="A311" s="13" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" ht="15">
+      <c r="A313" s="12" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1">
+      <c r="A315" s="13" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1">
+      <c r="A316" s="13" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1">
+      <c r="A317" s="13" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1">
+      <c r="A318" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1">
+      <c r="A319" s="14"/>
+    </row>
+    <row r="320" spans="1:1">
+      <c r="A320" s="13" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1">
+      <c r="A321" s="13" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1">
+      <c r="A322" s="13" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1">
+      <c r="A323" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1">
+      <c r="A324" s="14"/>
+    </row>
+    <row r="325" spans="1:1">
+      <c r="A325" s="13" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1">
+      <c r="A326" s="13" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1">
+      <c r="A327" s="13" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1">
+      <c r="A328" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1">
+      <c r="A329" s="14"/>
+    </row>
+    <row r="330" spans="1:1">
+      <c r="A330" s="13" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1">
+      <c r="A331" s="13" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1">
+      <c r="A332" s="13" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1">
+      <c r="A333" s="13" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1">
+      <c r="A334" s="13" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1">
+      <c r="A335" s="14"/>
+    </row>
+    <row r="336" spans="1:1">
+      <c r="A336" s="13" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1">
+      <c r="A337" s="13" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1">
+      <c r="A338" s="13" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1">
+      <c r="A339" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" ht="15">
+      <c r="A341" s="16" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1">
+      <c r="A342" s="14"/>
+    </row>
+    <row r="343" spans="1:1">
+      <c r="A343" s="14" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1">
+      <c r="A344" s="14" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1">
+      <c r="A345" s="14" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1">
+      <c r="A346" s="14" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" ht="15">
+      <c r="A348" s="12" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1">
+      <c r="A350" s="13" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1">
+      <c r="A351" s="13" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1">
+      <c r="A352" s="13" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1">
+      <c r="A353" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1">
+      <c r="A354" s="14"/>
+    </row>
+    <row r="355" spans="1:1">
+      <c r="A355" s="13" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1">
+      <c r="A356" s="13" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1">
+      <c r="A357" s="14"/>
+    </row>
+    <row r="358" spans="1:1">
+      <c r="A358" s="13" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1">
+      <c r="A359" s="13" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" ht="15">
+      <c r="A361" s="12" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1">
+      <c r="A363" s="13" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1">
+      <c r="A364" s="13" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1">
+      <c r="A365" s="13" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1">
+      <c r="A366" s="13" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1">
+      <c r="A367" s="14"/>
+    </row>
+    <row r="368" spans="1:1">
+      <c r="A368" s="13" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1">
+      <c r="A369" s="13" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1">
+      <c r="A370" s="13" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1">
+      <c r="A371" s="13" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1">
+      <c r="A372" s="14"/>
+    </row>
+    <row r="373" spans="1:1">
+      <c r="A373" s="13" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1">
+      <c r="A374" s="13" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1">
+      <c r="A375" s="13" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1">
+      <c r="A376" s="13" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1">
+      <c r="A377" s="13" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1">
+      <c r="A378" s="13" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1" ht="15">
+      <c r="A382" s="12" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1" ht="15">
+      <c r="A384" s="12" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1">
+      <c r="A386" s="13" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1">
+      <c r="A387" s="13" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1">
+      <c r="A388" s="13" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1">
+      <c r="A389" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1">
+      <c r="A390" s="14"/>
+    </row>
+    <row r="391" spans="1:1">
+      <c r="A391" s="13" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1">
+      <c r="A392" s="13" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1" ht="15">
+      <c r="A394" s="16" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1">
+      <c r="A395" s="14"/>
+    </row>
+    <row r="396" spans="1:1">
+      <c r="A396" s="14" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1">
+      <c r="A397" s="14" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1">
+      <c r="A398" s="14" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1" ht="15">
+      <c r="A400" s="12" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1">
+      <c r="A402" s="13" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1">
+      <c r="A403" s="13" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1">
+      <c r="A404" s="13" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1">
+      <c r="A405" s="14"/>
+    </row>
+    <row r="406" spans="1:1">
+      <c r="A406" s="13" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1">
+      <c r="A407" s="13" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1">
+      <c r="A408" s="14"/>
+    </row>
+    <row r="409" spans="1:1">
+      <c r="A409" s="13" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1">
+      <c r="A410" s="13" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1">
+      <c r="A411" s="14"/>
+    </row>
+    <row r="412" spans="1:1">
+      <c r="A412" s="13" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1">
+      <c r="A413" s="13" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1">
+      <c r="A414" s="14"/>
+    </row>
+    <row r="415" spans="1:1">
+      <c r="A415" s="13" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1">
+      <c r="A416" s="13" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1">
+      <c r="A417" s="13" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1">
+      <c r="A418" s="13" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1">
+      <c r="A419" s="13" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1">
+      <c r="A420" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1">
+      <c r="A421" s="14"/>
+    </row>
+    <row r="422" spans="1:1">
+      <c r="A422" s="13" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1">
+      <c r="A423" s="13" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1">
+      <c r="A424" s="13" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1" ht="15">
+      <c r="A426" s="12" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1">
+      <c r="A428" s="13" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1">
+      <c r="A429" s="13" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1">
+      <c r="A430" s="13" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1">
+      <c r="A431" s="14"/>
+    </row>
+    <row r="432" spans="1:1">
+      <c r="A432" s="13" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1">
+      <c r="A433" s="13" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1">
+      <c r="A434" s="13" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1">
+      <c r="A435" s="14"/>
+    </row>
+    <row r="436" spans="1:1">
+      <c r="A436" s="13" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1">
+      <c r="A437" s="13" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1">
+      <c r="A438" s="13" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1">
+      <c r="A439" s="13" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1">
+      <c r="A440" s="13" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1">
+      <c r="A441" s="13" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1">
+      <c r="A442" s="14"/>
+    </row>
+    <row r="443" spans="1:1">
+      <c r="A443" s="13" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1">
+      <c r="A444" s="13" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1">
+      <c r="A445" s="13" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1">
+      <c r="A446" s="13" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1">
+      <c r="A447" s="14"/>
+    </row>
+    <row r="448" spans="1:1">
+      <c r="A448" s="13" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1">
+      <c r="A449" s="13" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1">
+      <c r="A450" s="13" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1" ht="15">
+      <c r="A452" s="16" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1">
+      <c r="A454" s="13" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1">
+      <c r="A455" s="13" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1">
+      <c r="A456" s="13" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1">
+      <c r="A457" s="14"/>
+    </row>
+    <row r="458" spans="1:1">
+      <c r="A458" s="13" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1">
+      <c r="A459" s="13" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1" ht="15">
+      <c r="A461" s="12" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1">
+      <c r="A463" s="13" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1">
+      <c r="A464" s="14"/>
+    </row>
+    <row r="465" spans="1:1">
+      <c r="A465" s="13" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1">
+      <c r="A466" s="13" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1">
+      <c r="A467" s="14"/>
+    </row>
+    <row r="468" spans="1:1">
+      <c r="A468" s="13" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1">
+      <c r="A469" s="13" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1">
+      <c r="A470" s="14"/>
+    </row>
+    <row r="471" spans="1:1">
+      <c r="A471" s="13" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1">
+      <c r="A472" s="13" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1">
+      <c r="A473" s="14"/>
+    </row>
+    <row r="474" spans="1:1">
+      <c r="A474" s="13" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1">
+      <c r="A475" s="13" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1">
+      <c r="A476" s="13" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1">
+      <c r="A477" s="13" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1">
+      <c r="A478" s="13" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1">
+      <c r="A479" s="13" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1">
+      <c r="A480" s="13" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1">
+      <c r="A481" s="13" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1">
+      <c r="A482" s="13" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1">
+      <c r="A483" s="13" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1">
+      <c r="A484" s="13" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1">
+      <c r="A485" s="13" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1" ht="15">
+      <c r="A489" s="12" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1" ht="15">
+      <c r="A491" s="12" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1" ht="15">
+      <c r="A493" s="12" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1">
+      <c r="A495" s="13" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1">
+      <c r="A496" s="13" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="497" spans="1:1">
+      <c r="A497" s="13" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="498" spans="1:1">
+      <c r="A498" s="13" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="499" spans="1:1">
+      <c r="A499" s="14"/>
+    </row>
+    <row r="500" spans="1:1">
+      <c r="A500" s="13" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="501" spans="1:1">
+      <c r="A501" s="13" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="502" spans="1:1">
+      <c r="A502" s="13" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="503" spans="1:1">
+      <c r="A503" s="14"/>
+    </row>
+    <row r="504" spans="1:1">
+      <c r="A504" s="13" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="505" spans="1:1">
+      <c r="A505" s="13" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="507" spans="1:1" ht="15">
+      <c r="A507" s="12" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="509" spans="1:1">
+      <c r="A509" s="13" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="510" spans="1:1">
+      <c r="A510" s="13" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="511" spans="1:1">
+      <c r="A511" s="13" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="512" spans="1:1">
+      <c r="A512" s="13" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="513" spans="1:1">
+      <c r="A513" s="14"/>
+    </row>
+    <row r="514" spans="1:1">
+      <c r="A514" s="13" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="515" spans="1:1">
+      <c r="A515" s="13" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="516" spans="1:1">
+      <c r="A516" s="13" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="517" spans="1:1">
+      <c r="A517" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="518" spans="1:1">
+      <c r="A518" s="14"/>
+    </row>
+    <row r="519" spans="1:1">
+      <c r="A519" s="13" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="520" spans="1:1">
+      <c r="A520" s="13" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="521" spans="1:1">
+      <c r="A521" s="14"/>
+    </row>
+    <row r="522" spans="1:1">
+      <c r="A522" s="13" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="523" spans="1:1">
+      <c r="A523" s="13" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="525" spans="1:1" ht="15">
+      <c r="A525" s="12" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="527" spans="1:1">
+      <c r="A527" s="13" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="528" spans="1:1">
+      <c r="A528" s="13" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="529" spans="1:1">
+      <c r="A529" s="14"/>
+    </row>
+    <row r="530" spans="1:1">
+      <c r="A530" s="13" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="531" spans="1:1">
+      <c r="A531" s="13" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="532" spans="1:1">
+      <c r="A532" s="13" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="533" spans="1:1">
+      <c r="A533" s="13" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="534" spans="1:1">
+      <c r="A534" s="13" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="535" spans="1:1">
+      <c r="A535" s="14"/>
+    </row>
+    <row r="536" spans="1:1">
+      <c r="A536" s="13" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="537" spans="1:1">
+      <c r="A537" s="13" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="538" spans="1:1">
+      <c r="A538" s="14"/>
+    </row>
+    <row r="539" spans="1:1">
+      <c r="A539" s="13" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="540" spans="1:1">
+      <c r="A540" s="13" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="541" spans="1:1">
+      <c r="A541" s="13" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="542" spans="1:1">
+      <c r="A542" s="13" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="543" spans="1:1">
+      <c r="A543" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="544" spans="1:1">
+      <c r="A544" s="14"/>
+    </row>
+    <row r="545" spans="1:1">
+      <c r="A545" s="13" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="546" spans="1:1">
+      <c r="A546" s="13" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="547" spans="1:1">
+      <c r="A547" s="13" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="548" spans="1:1">
+      <c r="A548" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="549" spans="1:1">
+      <c r="A549" s="13" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="550" spans="1:1">
+      <c r="A550" s="14"/>
+    </row>
+    <row r="551" spans="1:1">
+      <c r="A551" s="13" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="552" spans="1:1">
+      <c r="A552" s="13" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="554" spans="1:1" ht="15">
+      <c r="A554" s="12" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="556" spans="1:1">
+      <c r="A556" s="13" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="557" spans="1:1">
+      <c r="A557" s="14"/>
+    </row>
+    <row r="558" spans="1:1">
+      <c r="A558" s="13" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="559" spans="1:1">
+      <c r="A559" s="13" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="560" spans="1:1">
+      <c r="A560" s="13" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="561" spans="1:1">
+      <c r="A561" s="13" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="562" spans="1:1">
+      <c r="A562" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="563" spans="1:1">
+      <c r="A563" s="14"/>
+    </row>
+    <row r="564" spans="1:1">
+      <c r="A564" s="13" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="565" spans="1:1">
+      <c r="A565" s="14"/>
+    </row>
+    <row r="566" spans="1:1">
+      <c r="A566" s="13" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="567" spans="1:1">
+      <c r="A567" s="13" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="568" spans="1:1">
+      <c r="A568" s="13" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="569" spans="1:1">
+      <c r="A569" s="13" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="570" spans="1:1">
+      <c r="A570" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="571" spans="1:1">
+      <c r="A571" s="14"/>
+    </row>
+    <row r="572" spans="1:1">
+      <c r="A572" s="13" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="573" spans="1:1">
+      <c r="A573" s="13" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="574" spans="1:1">
+      <c r="A574" s="13" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="575" spans="1:1">
+      <c r="A575" s="13" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="579" spans="1:1" ht="15">
+      <c r="A579" s="12" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="581" spans="1:1" ht="15">
+      <c r="A581" s="12" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="583" spans="1:1">
+      <c r="A583" s="13" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="584" spans="1:1">
+      <c r="A584" s="13" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="585" spans="1:1">
+      <c r="A585" s="13" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="586" spans="1:1">
+      <c r="A586" s="13" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="587" spans="1:1">
+      <c r="A587" s="14"/>
+    </row>
+    <row r="588" spans="1:1">
+      <c r="A588" s="13" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="589" spans="1:1">
+      <c r="A589" s="13" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="590" spans="1:1">
+      <c r="A590" s="13" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="591" spans="1:1">
+      <c r="A591" s="13" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="592" spans="1:1">
+      <c r="A592" s="13" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="593" spans="1:1">
+      <c r="A593" s="14"/>
+    </row>
+    <row r="594" spans="1:1">
+      <c r="A594" s="13" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="595" spans="1:1">
+      <c r="A595" s="13" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="596" spans="1:1">
+      <c r="A596" s="13" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="598" spans="1:1" ht="15">
+      <c r="A598" s="16" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="600" spans="1:1" ht="15">
+      <c r="A600" s="12" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="602" spans="1:1">
+      <c r="A602" s="13" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="603" spans="1:1">
+      <c r="A603" s="14"/>
+    </row>
+    <row r="604" spans="1:1">
+      <c r="A604" s="13" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="605" spans="1:1">
+      <c r="A605" s="13" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="606" spans="1:1">
+      <c r="A606" s="13" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="607" spans="1:1">
+      <c r="A607" s="13" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="608" spans="1:1">
+      <c r="A608" s="14"/>
+    </row>
+    <row r="609" spans="1:1">
+      <c r="A609" s="13" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="610" spans="1:1">
+      <c r="A610" s="13" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="611" spans="1:1">
+      <c r="A611" s="13" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="612" spans="1:1">
+      <c r="A612" s="14"/>
+    </row>
+    <row r="613" spans="1:1">
+      <c r="A613" s="13" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="614" spans="1:1">
+      <c r="A614" s="13" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="615" spans="1:1">
+      <c r="A615" s="13" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="616" spans="1:1">
+      <c r="A616" s="13" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="617" spans="1:1">
+      <c r="A617" s="14"/>
+    </row>
+    <row r="618" spans="1:1">
+      <c r="A618" s="13" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="619" spans="1:1">
+      <c r="A619" s="13" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="620" spans="1:1">
+      <c r="A620" s="13" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="622" spans="1:1" ht="15">
+      <c r="A622" s="12" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="624" spans="1:1">
+      <c r="A624" s="13" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="625" spans="1:1">
+      <c r="A625" s="14"/>
+    </row>
+    <row r="626" spans="1:1">
+      <c r="A626" s="13" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="627" spans="1:1">
+      <c r="A627" s="13" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="628" spans="1:1">
+      <c r="A628" s="13" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="629" spans="1:1">
+      <c r="A629" s="13" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="630" spans="1:1">
+      <c r="A630" s="14"/>
+    </row>
+    <row r="631" spans="1:1">
+      <c r="A631" s="13" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="632" spans="1:1">
+      <c r="A632" s="13" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="633" spans="1:1">
+      <c r="A633" s="13" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="634" spans="1:1">
+      <c r="A634" s="14"/>
+    </row>
+    <row r="635" spans="1:1">
+      <c r="A635" s="13" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="636" spans="1:1">
+      <c r="A636" s="13" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="637" spans="1:1">
+      <c r="A637" s="13" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="638" spans="1:1">
+      <c r="A638" s="13" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="639" spans="1:1">
+      <c r="A639" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="640" spans="1:1">
+      <c r="A640" s="14"/>
+    </row>
+    <row r="641" spans="1:1">
+      <c r="A641" s="13" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="642" spans="1:1">
+      <c r="A642" s="14"/>
+    </row>
+    <row r="643" spans="1:1">
+      <c r="A643" s="13" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="644" spans="1:1">
+      <c r="A644" s="13" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="645" spans="1:1">
+      <c r="A645" s="14"/>
+    </row>
+    <row r="646" spans="1:1">
+      <c r="A646" s="13" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="647" spans="1:1">
+      <c r="A647" s="13" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="648" spans="1:1">
+      <c r="A648" s="13" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="649" spans="1:1">
+      <c r="A649" s="14"/>
+    </row>
+    <row r="650" spans="1:1">
+      <c r="A650" s="13" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="651" spans="1:1">
+      <c r="A651" s="13" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="652" spans="1:1">
+      <c r="A652" s="13" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="654" spans="1:1" ht="15">
+      <c r="A654" s="12" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="656" spans="1:1">
+      <c r="A656" s="13" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="657" spans="1:1">
+      <c r="A657" s="13" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="658" spans="1:1">
+      <c r="A658" s="14"/>
+    </row>
+    <row r="659" spans="1:1">
+      <c r="A659" s="13" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="660" spans="1:1">
+      <c r="A660" s="13" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="661" spans="1:1">
+      <c r="A661" s="14"/>
+    </row>
+    <row r="662" spans="1:1">
+      <c r="A662" s="13" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="663" spans="1:1">
+      <c r="A663" s="13" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="664" spans="1:1">
+      <c r="A664" s="13" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="665" spans="1:1">
+      <c r="A665" s="13" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="666" spans="1:1">
+      <c r="A666" s="13" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="667" spans="1:1">
+      <c r="A667" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="668" spans="1:1">
+      <c r="A668" s="13" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="669" spans="1:1">
+      <c r="A669" s="14"/>
+    </row>
+    <row r="670" spans="1:1">
+      <c r="A670" s="13" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="671" spans="1:1">
+      <c r="A671" s="13" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="675" spans="1:1" ht="15">
+      <c r="A675" s="12" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="677" spans="1:1" ht="15">
+      <c r="A677" s="12" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="679" spans="1:1">
+      <c r="A679" s="13" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="680" spans="1:1">
+      <c r="A680" s="13" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="681" spans="1:1">
+      <c r="A681" s="13" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="682" spans="1:1">
+      <c r="A682" s="14"/>
+    </row>
+    <row r="683" spans="1:1">
+      <c r="A683" s="13" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="684" spans="1:1">
+      <c r="A684" s="13" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="685" spans="1:1">
+      <c r="A685" s="13" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="687" spans="1:1" ht="15">
+      <c r="A687" s="12" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="689" spans="1:1">
+      <c r="A689" s="13" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="690" spans="1:1">
+      <c r="A690" s="13" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="691" spans="1:1">
+      <c r="A691" s="14"/>
+    </row>
+    <row r="692" spans="1:1">
+      <c r="A692" s="13" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="694" spans="1:1" ht="15">
+      <c r="A694" s="12" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="696" spans="1:1">
+      <c r="A696" s="13" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="697" spans="1:1">
+      <c r="A697" s="13" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="698" spans="1:1">
+      <c r="A698" s="13" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="699" spans="1:1">
+      <c r="A699" s="13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="701" spans="1:1" ht="15">
+      <c r="A701" s="12" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="703" spans="1:1">
+      <c r="A703" s="13" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="704" spans="1:1">
+      <c r="A704" s="13" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="706" spans="1:1" ht="15">
+      <c r="A706" s="12" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="708" spans="1:1">
+      <c r="A708" s="13" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="709" spans="1:1">
+      <c r="A709" s="13" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="710" spans="1:1">
+      <c r="A710" s="14"/>
+    </row>
+    <row r="711" spans="1:1">
+      <c r="A711" s="13" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="712" spans="1:1">
+      <c r="A712" s="13" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="716" spans="1:1" ht="15">
+      <c r="A716" s="12" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="717" spans="1:1">
+      <c r="A717" s="14"/>
+    </row>
+    <row r="718" spans="1:1" ht="15">
+      <c r="A718" s="12" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="719" spans="1:1" ht="15">
+      <c r="A719" s="12" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="720" spans="1:1" ht="15">
+      <c r="A720" s="12" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="721" spans="1:1" ht="15">
+      <c r="A721" s="12" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="722" spans="1:1" ht="15">
+      <c r="A722" s="12" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="723" spans="1:1" ht="15">
+      <c r="A723" s="12" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="724" spans="1:1" ht="15">
+      <c r="A724" s="12" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="728" spans="1:1" ht="15">
+      <c r="A728" s="16" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="729" spans="1:1">
+      <c r="A729" s="14"/>
+    </row>
+    <row r="730" spans="1:1">
+      <c r="A730" s="14" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="731" spans="1:1">
+      <c r="A731" s="14" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="732" spans="1:1">
+      <c r="A732" s="14" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="733" spans="1:1">
+      <c r="A733" s="14" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="734" spans="1:1">
+      <c r="A734" s="14" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="735" spans="1:1">
+      <c r="A735" s="14" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>